--- a/data/import_diem_chuan.xlsx
+++ b/data/import_diem_chuan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chat-bot-tuyen-sinh\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352206F1-A0CE-40A8-888A-2A0BE37C0381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98251EA5-88BE-4C73-B12C-C7EE1016F7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5E48B358-080F-4AF0-A56B-5A126673D87A}"/>
   </bookViews>
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -682,6 +682,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1016,10 +1023,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A16004-149F-469E-9454-450BC0FDCCAF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O912"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" customWidth="1"/>
@@ -1032,7 +1040,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>186</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1078,7 +1086,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>7140114</v>
       </c>
@@ -1105,7 +1113,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>7140202</v>
       </c>
@@ -1132,7 +1140,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>7140205</v>
       </c>
@@ -1159,7 +1167,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>7140208</v>
       </c>
@@ -1186,7 +1194,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>7140209</v>
       </c>
@@ -1213,7 +1221,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>7140210</v>
       </c>
@@ -1240,7 +1248,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7140211</v>
       </c>
@@ -1267,7 +1275,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7140212</v>
       </c>
@@ -1294,7 +1302,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7140213</v>
       </c>
@@ -1321,7 +1329,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7140217</v>
       </c>
@@ -1348,7 +1356,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>7140218</v>
       </c>
@@ -1375,7 +1383,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>7140219</v>
       </c>
@@ -1402,7 +1410,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>7140231</v>
       </c>
@@ -1429,7 +1437,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>7220201</v>
       </c>
@@ -1456,7 +1464,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>7229042</v>
       </c>
@@ -1483,7 +1491,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>7310101</v>
       </c>
@@ -1510,7 +1518,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>7310201</v>
       </c>
@@ -1537,7 +1545,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>7310205</v>
       </c>
@@ -1564,7 +1572,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>7310630</v>
       </c>
@@ -1591,7 +1599,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>7340101</v>
       </c>
@@ -1618,7 +1626,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>7340201</v>
       </c>
@@ -1645,7 +1653,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>7340301</v>
       </c>
@@ -1672,7 +1680,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>7380101</v>
       </c>
@@ -1699,7 +1707,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>7380107</v>
       </c>
@@ -1726,7 +1734,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>7420201</v>
       </c>
@@ -1753,7 +1761,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>7480101</v>
       </c>
@@ -1780,7 +1788,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>7480201</v>
       </c>
@@ -1807,7 +1815,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>7510205</v>
       </c>
@@ -1834,7 +1842,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>7510206</v>
       </c>
@@ -1861,7 +1869,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>7510301</v>
       </c>
@@ -1888,7 +1896,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>7520207</v>
       </c>
@@ -1915,7 +1923,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>7520216</v>
       </c>
@@ -1942,7 +1950,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>7540101</v>
       </c>
@@ -1969,7 +1977,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>7580201</v>
       </c>
@@ -1996,7 +2004,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>7580205</v>
       </c>
@@ -2023,7 +2031,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>7580301</v>
       </c>
@@ -2050,7 +2058,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>7620105</v>
       </c>
@@ -2077,7 +2085,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>7620109</v>
       </c>
@@ -2104,7 +2112,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>7620301</v>
       </c>
@@ -2131,7 +2139,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>7720301</v>
       </c>
@@ -2158,7 +2166,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>7760101</v>
       </c>
@@ -2185,7 +2193,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>7850101</v>
       </c>
@@ -2212,7 +2220,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>7850103</v>
       </c>
@@ -2239,7 +2247,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>57</v>
       </c>
@@ -2266,7 +2274,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>59</v>
       </c>
@@ -2293,7 +2301,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -2320,7 +2328,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
@@ -2347,7 +2355,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>7140114</v>
       </c>
@@ -2374,7 +2382,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>7140202</v>
       </c>
@@ -2401,7 +2409,7 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>7140205</v>
       </c>
@@ -2428,7 +2436,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>7140208</v>
       </c>
@@ -2455,7 +2463,7 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>7140209</v>
       </c>
@@ -2482,7 +2490,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>7140210</v>
       </c>
@@ -2509,7 +2517,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>7140211</v>
       </c>
@@ -2536,7 +2544,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>7140212</v>
       </c>
@@ -2563,7 +2571,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>7140213</v>
       </c>
@@ -2590,7 +2598,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>7140217</v>
       </c>
@@ -2617,7 +2625,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>7140218</v>
       </c>
@@ -2644,7 +2652,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>7140219</v>
       </c>
@@ -2671,7 +2679,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>7140231</v>
       </c>
@@ -2698,7 +2706,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>7220201</v>
       </c>
@@ -2725,7 +2733,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>7229042</v>
       </c>
@@ -2752,7 +2760,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>7310101</v>
       </c>
@@ -2779,7 +2787,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>7310201</v>
       </c>
@@ -2806,7 +2814,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>7310205</v>
       </c>
@@ -2833,7 +2841,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>7310630</v>
       </c>
@@ -2860,7 +2868,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>7340101</v>
       </c>
@@ -2887,7 +2895,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>7340201</v>
       </c>
@@ -2914,7 +2922,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>7340301</v>
       </c>
@@ -2941,7 +2949,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>7380101</v>
       </c>
@@ -2968,7 +2976,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>7380107</v>
       </c>
@@ -2995,7 +3003,7 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>7420201</v>
       </c>
@@ -3022,7 +3030,7 @@
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>7480101</v>
       </c>
@@ -3049,7 +3057,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>7480201</v>
       </c>
@@ -3076,7 +3084,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>7510205</v>
       </c>
@@ -3103,7 +3111,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>7510206</v>
       </c>
@@ -3130,7 +3138,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>7510301</v>
       </c>
@@ -3157,7 +3165,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>7520207</v>
       </c>
@@ -3184,7 +3192,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>7520216</v>
       </c>
@@ -3211,7 +3219,7 @@
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>7540101</v>
       </c>
@@ -3238,7 +3246,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>7580201</v>
       </c>
@@ -3265,7 +3273,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>7580205</v>
       </c>
@@ -3292,7 +3300,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>7580301</v>
       </c>
@@ -3319,7 +3327,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>7620105</v>
       </c>
@@ -3346,7 +3354,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>7620109</v>
       </c>
@@ -3373,7 +3381,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>7620301</v>
       </c>
@@ -3400,7 +3408,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>7720301</v>
       </c>
@@ -3427,7 +3435,7 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>7760101</v>
       </c>
@@ -3454,7 +3462,7 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>7850101</v>
       </c>
@@ -3481,7 +3489,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>7850103</v>
       </c>
@@ -3508,7 +3516,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>60</v>
       </c>
@@ -3535,7 +3543,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>7220201</v>
       </c>
@@ -3562,7 +3570,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>7229042</v>
       </c>
@@ -3589,7 +3597,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>7310101</v>
       </c>
@@ -3616,7 +3624,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>7310201</v>
       </c>
@@ -3643,7 +3651,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>7310205</v>
       </c>
@@ -3670,7 +3678,7 @@
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>7310630</v>
       </c>
@@ -3697,7 +3705,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>7340201</v>
       </c>
@@ -3724,7 +3732,7 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>7340301</v>
       </c>
@@ -3751,7 +3759,7 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>7380101</v>
       </c>
@@ -3778,7 +3786,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>7380107</v>
       </c>
@@ -3805,7 +3813,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>7420201</v>
       </c>
@@ -3832,7 +3840,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>7480101</v>
       </c>
@@ -3859,7 +3867,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>7510205</v>
       </c>
@@ -3886,7 +3894,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>7510206</v>
       </c>
@@ -3913,7 +3921,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>7510301</v>
       </c>
@@ -3940,7 +3948,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>7520207</v>
       </c>
@@ -3967,7 +3975,7 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>7520216</v>
       </c>
@@ -3994,7 +4002,7 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>7540101</v>
       </c>
@@ -4021,7 +4029,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>7580201</v>
       </c>
@@ -4048,7 +4056,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>7580205</v>
       </c>
@@ -4075,7 +4083,7 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>7580301</v>
       </c>
@@ -4102,7 +4110,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>7620105</v>
       </c>
@@ -4129,7 +4137,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>7620109</v>
       </c>
@@ -4156,7 +4164,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>7620301</v>
       </c>
@@ -4183,7 +4191,7 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>7760101</v>
       </c>
@@ -4210,7 +4218,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>7850101</v>
       </c>
@@ -4237,7 +4245,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>7850103</v>
       </c>
@@ -4264,7 +4272,7 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>60</v>
       </c>
@@ -4291,7 +4299,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>61</v>
       </c>
@@ -4318,7 +4326,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>7140201</v>
       </c>
@@ -4345,7 +4353,7 @@
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>7140206</v>
       </c>
@@ -4372,7 +4380,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>7140201</v>
       </c>
@@ -4399,7 +4407,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>7140206</v>
       </c>
@@ -4426,7 +4434,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>7140114</v>
       </c>
@@ -4453,7 +4461,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>7140202</v>
       </c>
@@ -4480,7 +4488,7 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>7140205</v>
       </c>
@@ -4507,7 +4515,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>7140208</v>
       </c>
@@ -4534,7 +4542,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>7140209</v>
       </c>
@@ -4561,7 +4569,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>7140210</v>
       </c>
@@ -4588,7 +4596,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>7140211</v>
       </c>
@@ -4615,7 +4623,7 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>7140212</v>
       </c>
@@ -4644,7 +4652,7 @@
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>7140212</v>
       </c>
@@ -4673,7 +4681,7 @@
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>7140212</v>
       </c>
@@ -4702,7 +4710,7 @@
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>7140212</v>
       </c>
@@ -4731,7 +4739,7 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>7140213</v>
       </c>
@@ -4758,7 +4766,7 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>7140217</v>
       </c>
@@ -4785,7 +4793,7 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>7140218</v>
       </c>
@@ -4812,7 +4820,7 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>7140219</v>
       </c>
@@ -4839,7 +4847,7 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>7140231</v>
       </c>
@@ -4866,7 +4874,7 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>7140247</v>
       </c>
@@ -4893,7 +4901,7 @@
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>7140249</v>
       </c>
@@ -4920,7 +4928,7 @@
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>7220201</v>
       </c>
@@ -4947,7 +4955,7 @@
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>7229042</v>
       </c>
@@ -4974,7 +4982,7 @@
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>7310101</v>
       </c>
@@ -5001,7 +5009,7 @@
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>7310109</v>
       </c>
@@ -5028,7 +5036,7 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>7310201</v>
       </c>
@@ -5055,7 +5063,7 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>7310205</v>
       </c>
@@ -5082,7 +5090,7 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>7310403</v>
       </c>
@@ -5109,7 +5117,7 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>7310601</v>
       </c>
@@ -5136,7 +5144,7 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>7310630</v>
       </c>
@@ -5163,7 +5171,7 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>7340101</v>
       </c>
@@ -5190,7 +5198,7 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>7340122</v>
       </c>
@@ -5217,7 +5225,7 @@
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>7340201</v>
       </c>
@@ -5244,7 +5252,7 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>7340301</v>
       </c>
@@ -5271,7 +5279,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>7380101</v>
       </c>
@@ -5298,7 +5306,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>7380107</v>
       </c>
@@ -5325,7 +5333,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>7420201</v>
       </c>
@@ -5352,7 +5360,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>7480101</v>
       </c>
@@ -5379,7 +5387,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>7480201</v>
       </c>
@@ -5406,7 +5414,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>7510205</v>
       </c>
@@ -5433,7 +5441,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>7510206</v>
       </c>
@@ -5460,7 +5468,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>7510301</v>
       </c>
@@ -5487,7 +5495,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>7520207</v>
       </c>
@@ -5514,7 +5522,7 @@
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>7520216</v>
       </c>
@@ -5541,7 +5549,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>7540101</v>
       </c>
@@ -5568,7 +5576,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>7580101</v>
       </c>
@@ -5595,7 +5603,7 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>7580201</v>
       </c>
@@ -5622,7 +5630,7 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>7580205</v>
       </c>
@@ -5649,7 +5657,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>7580301</v>
       </c>
@@ -5676,7 +5684,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>7620105</v>
       </c>
@@ -5703,7 +5711,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>7620109</v>
       </c>
@@ -5730,7 +5738,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>7620110</v>
       </c>
@@ -5757,7 +5765,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>7620301</v>
       </c>
@@ -5784,7 +5792,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>7640101</v>
       </c>
@@ -5811,7 +5819,7 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>7720301</v>
       </c>
@@ -5838,7 +5846,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>7760101</v>
       </c>
@@ -5865,7 +5873,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>7850101</v>
       </c>
@@ -5892,7 +5900,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>7850103</v>
       </c>
@@ -5919,7 +5927,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>57</v>
       </c>
@@ -5946,7 +5954,7 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>59</v>
       </c>
@@ -5973,7 +5981,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>60</v>
       </c>
@@ -6000,7 +6008,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>61</v>
       </c>
@@ -6027,7 +6035,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>7140114</v>
       </c>
@@ -6054,7 +6062,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>7220201</v>
       </c>
@@ -6081,7 +6089,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>7229042</v>
       </c>
@@ -6108,7 +6116,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>7310101</v>
       </c>
@@ -6135,7 +6143,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>7310109</v>
       </c>
@@ -6162,7 +6170,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>7310201</v>
       </c>
@@ -6189,7 +6197,7 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>7310205</v>
       </c>
@@ -6216,7 +6224,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>7310403</v>
       </c>
@@ -6243,7 +6251,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>7310601</v>
       </c>
@@ -6270,7 +6278,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>7310630</v>
       </c>
@@ -6297,7 +6305,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>7340101</v>
       </c>
@@ -6324,7 +6332,7 @@
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>7340122</v>
       </c>
@@ -6351,7 +6359,7 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>7340201</v>
       </c>
@@ -6378,7 +6386,7 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>7340301</v>
       </c>
@@ -6405,7 +6413,7 @@
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>7380101</v>
       </c>
@@ -6432,7 +6440,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>7380107</v>
       </c>
@@ -6459,7 +6467,7 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>7420201</v>
       </c>
@@ -6486,7 +6494,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>7480101</v>
       </c>
@@ -6513,7 +6521,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>7480201</v>
       </c>
@@ -6540,7 +6548,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>7510205</v>
       </c>
@@ -6567,7 +6575,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>7510206</v>
       </c>
@@ -6594,7 +6602,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>7510301</v>
       </c>
@@ -6621,7 +6629,7 @@
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>7520207</v>
       </c>
@@ -6648,7 +6656,7 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>7520216</v>
       </c>
@@ -6675,7 +6683,7 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>7540101</v>
       </c>
@@ -6702,7 +6710,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>7580101</v>
       </c>
@@ -6729,7 +6737,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>7580201</v>
       </c>
@@ -6756,7 +6764,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>7580205</v>
       </c>
@@ -6783,7 +6791,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>7580301</v>
       </c>
@@ -6810,7 +6818,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>7620105</v>
       </c>
@@ -6837,7 +6845,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>7620109</v>
       </c>
@@ -6864,7 +6872,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>7620110</v>
       </c>
@@ -6891,7 +6899,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>7620301</v>
       </c>
@@ -6918,7 +6926,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>7640101</v>
       </c>
@@ -6945,7 +6953,7 @@
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>7720301</v>
       </c>
@@ -6972,7 +6980,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>7760101</v>
       </c>
@@ -6999,7 +7007,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>7850101</v>
       </c>
@@ -7026,7 +7034,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>7850103</v>
       </c>
@@ -7053,7 +7061,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>60</v>
       </c>
@@ -7080,7 +7088,7 @@
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>7140114</v>
       </c>
@@ -7107,7 +7115,7 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>7220201</v>
       </c>
@@ -7134,7 +7142,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>7229042</v>
       </c>
@@ -7161,7 +7169,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>7310101</v>
       </c>
@@ -7188,7 +7196,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>7310109</v>
       </c>
@@ -7215,7 +7223,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>7310201</v>
       </c>
@@ -7242,7 +7250,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>7310205</v>
       </c>
@@ -7269,7 +7277,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>7310403</v>
       </c>
@@ -7296,7 +7304,7 @@
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>7310601</v>
       </c>
@@ -7323,7 +7331,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>7310630</v>
       </c>
@@ -7350,7 +7358,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>7340101</v>
       </c>
@@ -7377,7 +7385,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>7340122</v>
       </c>
@@ -7404,7 +7412,7 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>7340201</v>
       </c>
@@ -7431,7 +7439,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>7340301</v>
       </c>
@@ -7458,7 +7466,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>7380101</v>
       </c>
@@ -7485,7 +7493,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>7380107</v>
       </c>
@@ -7512,7 +7520,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>7420201</v>
       </c>
@@ -7539,7 +7547,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>7480101</v>
       </c>
@@ -7566,7 +7574,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>7480201</v>
       </c>
@@ -7593,7 +7601,7 @@
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>7510205</v>
       </c>
@@ -7620,7 +7628,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>7510206</v>
       </c>
@@ -7647,7 +7655,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>7510301</v>
       </c>
@@ -7674,7 +7682,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>7520207</v>
       </c>
@@ -7701,7 +7709,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>7520216</v>
       </c>
@@ -7728,7 +7736,7 @@
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>7540101</v>
       </c>
@@ -7755,7 +7763,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>7580101</v>
       </c>
@@ -7782,7 +7790,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>7580201</v>
       </c>
@@ -7809,7 +7817,7 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>7580205</v>
       </c>
@@ -7836,7 +7844,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>7580301</v>
       </c>
@@ -7863,7 +7871,7 @@
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>7620105</v>
       </c>
@@ -7890,7 +7898,7 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>7620109</v>
       </c>
@@ -7917,7 +7925,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>7620110</v>
       </c>
@@ -7944,7 +7952,7 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>7620301</v>
       </c>
@@ -7971,7 +7979,7 @@
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>7640101</v>
       </c>
@@ -7998,7 +8006,7 @@
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>7720301</v>
       </c>
@@ -8025,7 +8033,7 @@
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>7760101</v>
       </c>
@@ -8052,7 +8060,7 @@
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>7850101</v>
       </c>
@@ -8079,7 +8087,7 @@
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>7850103</v>
       </c>
@@ -8106,7 +8114,7 @@
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>60</v>
       </c>
@@ -8133,7 +8141,7 @@
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>7140201</v>
       </c>
@@ -8160,7 +8168,7 @@
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>7140206</v>
       </c>
@@ -8187,7 +8195,7 @@
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>7580101</v>
       </c>
@@ -8214,7 +8222,7 @@
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>7140201</v>
       </c>
@@ -8241,7 +8249,7 @@
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>7140206</v>
       </c>
@@ -8268,7 +8276,7 @@
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>7580101</v>
       </c>
@@ -8295,7 +8303,7 @@
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>7140114</v>
       </c>
@@ -8324,7 +8332,7 @@
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>7140201</v>
       </c>
@@ -8353,7 +8361,7 @@
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>7140202</v>
       </c>
@@ -8382,7 +8390,7 @@
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>7140205</v>
       </c>
@@ -8411,7 +8419,7 @@
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>7140206</v>
       </c>
@@ -8440,7 +8448,7 @@
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>7140208</v>
       </c>
@@ -8469,7 +8477,7 @@
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>7140209</v>
       </c>
@@ -8498,7 +8506,7 @@
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>7140210</v>
       </c>
@@ -8527,7 +8535,7 @@
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>7140211</v>
       </c>
@@ -8556,7 +8564,7 @@
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>7140212</v>
       </c>
@@ -8585,7 +8593,7 @@
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>7140213</v>
       </c>
@@ -8614,7 +8622,7 @@
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>7140217</v>
       </c>
@@ -8643,7 +8651,7 @@
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>7140218</v>
       </c>
@@ -8672,7 +8680,7 @@
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>7140219</v>
       </c>
@@ -8701,7 +8709,7 @@
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>7140231</v>
       </c>
@@ -8730,7 +8738,7 @@
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>7140247</v>
       </c>
@@ -8759,7 +8767,7 @@
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>7140249</v>
       </c>
@@ -8788,7 +8796,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>7220201</v>
       </c>
@@ -8817,7 +8825,7 @@
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>7220204</v>
       </c>
@@ -8846,7 +8854,7 @@
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>7229042</v>
       </c>
@@ -8875,7 +8883,7 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>7310101</v>
       </c>
@@ -8904,7 +8912,7 @@
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>7310109</v>
       </c>
@@ -8933,7 +8941,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>7310201</v>
       </c>
@@ -8962,7 +8970,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>7310205</v>
       </c>
@@ -8991,7 +8999,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>7310403</v>
       </c>
@@ -9020,7 +9028,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>7310601</v>
       </c>
@@ -9049,7 +9057,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>7310630</v>
       </c>
@@ -9078,7 +9086,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>7340101</v>
       </c>
@@ -9107,7 +9115,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>7340122</v>
       </c>
@@ -9136,7 +9144,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>7340201</v>
       </c>
@@ -9165,7 +9173,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>7340205</v>
       </c>
@@ -9194,7 +9202,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>7340301</v>
       </c>
@@ -9223,7 +9231,7 @@
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>7380101</v>
       </c>
@@ -9252,7 +9260,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>7380102</v>
       </c>
@@ -9281,7 +9289,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>7380103</v>
       </c>
@@ -9310,7 +9318,7 @@
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>7380107</v>
       </c>
@@ -9339,7 +9347,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>7420201</v>
       </c>
@@ -9368,7 +9376,7 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>7480101</v>
       </c>
@@ -9397,7 +9405,7 @@
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>7480201</v>
       </c>
@@ -9426,7 +9434,7 @@
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>7510205</v>
       </c>
@@ -9455,7 +9463,7 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>7510206</v>
       </c>
@@ -9484,7 +9492,7 @@
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>7510301</v>
       </c>
@@ -9513,7 +9521,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>7510302</v>
       </c>
@@ -9542,7 +9550,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>7510303</v>
       </c>
@@ -9571,7 +9579,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>7520207</v>
       </c>
@@ -9600,7 +9608,7 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>7520216</v>
       </c>
@@ -9629,7 +9637,7 @@
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>7540101</v>
       </c>
@@ -9658,7 +9666,7 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>7580101</v>
       </c>
@@ -9687,7 +9695,7 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>7580101</v>
       </c>
@@ -9716,7 +9724,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>7580201</v>
       </c>
@@ -9745,7 +9753,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>7580205</v>
       </c>
@@ -9774,7 +9782,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>7580301</v>
       </c>
@@ -9803,7 +9811,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>7620105</v>
       </c>
@@ -9832,7 +9840,7 @@
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>7620109</v>
       </c>
@@ -9861,7 +9869,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>7620110</v>
       </c>
@@ -9890,7 +9898,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>7620301</v>
       </c>
@@ -9919,7 +9927,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>7640101</v>
       </c>
@@ -9948,7 +9956,7 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>7720301</v>
       </c>
@@ -9977,7 +9985,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>7760101</v>
       </c>
@@ -10006,7 +10014,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>7850101</v>
       </c>
@@ -10035,7 +10043,7 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>7850103</v>
       </c>
@@ -10064,7 +10072,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>137</v>
       </c>
@@ -10093,7 +10101,7 @@
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>138</v>
       </c>
@@ -10122,7 +10130,7 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>139</v>
       </c>
@@ -10151,7 +10159,7 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>140</v>
       </c>
@@ -10180,7 +10188,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>7140114</v>
       </c>
@@ -10209,7 +10217,7 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>7220201</v>
       </c>
@@ -10238,7 +10246,7 @@
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>7220204</v>
       </c>
@@ -10267,7 +10275,7 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>7229042</v>
       </c>
@@ -10296,7 +10304,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>7310101</v>
       </c>
@@ -10325,7 +10333,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>7310109</v>
       </c>
@@ -10354,7 +10362,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>7310201</v>
       </c>
@@ -10383,7 +10391,7 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>7310205</v>
       </c>
@@ -10412,7 +10420,7 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>7310403</v>
       </c>
@@ -10441,7 +10449,7 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>7310601</v>
       </c>
@@ -10470,7 +10478,7 @@
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>7310630</v>
       </c>
@@ -10499,7 +10507,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>7340101</v>
       </c>
@@ -10528,7 +10536,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>7340122</v>
       </c>
@@ -10557,7 +10565,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>7340201</v>
       </c>
@@ -10586,7 +10594,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>7340205</v>
       </c>
@@ -10615,7 +10623,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>7340301</v>
       </c>
@@ -10644,7 +10652,7 @@
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>7380101</v>
       </c>
@@ -10673,7 +10681,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>7380102</v>
       </c>
@@ -10702,7 +10710,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>7380103</v>
       </c>
@@ -10731,7 +10739,7 @@
       <c r="N352" s="1"/>
       <c r="O352" s="1"/>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>7380107</v>
       </c>
@@ -10760,7 +10768,7 @@
       <c r="N353" s="1"/>
       <c r="O353" s="1"/>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>7420201</v>
       </c>
@@ -10789,7 +10797,7 @@
       <c r="N354" s="1"/>
       <c r="O354" s="1"/>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>7480101</v>
       </c>
@@ -10818,7 +10826,7 @@
       <c r="N355" s="1"/>
       <c r="O355" s="1"/>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>7480201</v>
       </c>
@@ -10847,7 +10855,7 @@
       <c r="N356" s="1"/>
       <c r="O356" s="1"/>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>7510205</v>
       </c>
@@ -10876,7 +10884,7 @@
       <c r="N357" s="1"/>
       <c r="O357" s="1"/>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>7510206</v>
       </c>
@@ -10905,7 +10913,7 @@
       <c r="N358" s="1"/>
       <c r="O358" s="1"/>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>7510301</v>
       </c>
@@ -10934,7 +10942,7 @@
       <c r="N359" s="1"/>
       <c r="O359" s="1"/>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>7510302</v>
       </c>
@@ -10963,7 +10971,7 @@
       <c r="N360" s="1"/>
       <c r="O360" s="1"/>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>7510303</v>
       </c>
@@ -10992,7 +11000,7 @@
       <c r="N361" s="1"/>
       <c r="O361" s="1"/>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>7520207</v>
       </c>
@@ -11021,7 +11029,7 @@
       <c r="N362" s="1"/>
       <c r="O362" s="1"/>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>7520216</v>
       </c>
@@ -11050,7 +11058,7 @@
       <c r="N363" s="1"/>
       <c r="O363" s="1"/>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>7540101</v>
       </c>
@@ -11079,7 +11087,7 @@
       <c r="N364" s="1"/>
       <c r="O364" s="1"/>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>7580101</v>
       </c>
@@ -11108,7 +11116,7 @@
       <c r="N365" s="1"/>
       <c r="O365" s="1"/>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>7580101</v>
       </c>
@@ -11137,7 +11145,7 @@
       <c r="N366" s="1"/>
       <c r="O366" s="1"/>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>7580201</v>
       </c>
@@ -11166,7 +11174,7 @@
       <c r="N367" s="1"/>
       <c r="O367" s="1"/>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>7580205</v>
       </c>
@@ -11195,7 +11203,7 @@
       <c r="N368" s="1"/>
       <c r="O368" s="1"/>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>7580301</v>
       </c>
@@ -11224,7 +11232,7 @@
       <c r="N369" s="1"/>
       <c r="O369" s="1"/>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>7620105</v>
       </c>
@@ -11253,7 +11261,7 @@
       <c r="N370" s="1"/>
       <c r="O370" s="1"/>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>7620109</v>
       </c>
@@ -11282,7 +11290,7 @@
       <c r="N371" s="1"/>
       <c r="O371" s="1"/>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>7620110</v>
       </c>
@@ -11311,7 +11319,7 @@
       <c r="N372" s="1"/>
       <c r="O372" s="1"/>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>7620301</v>
       </c>
@@ -11340,7 +11348,7 @@
       <c r="N373" s="1"/>
       <c r="O373" s="1"/>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>7640101</v>
       </c>
@@ -11369,7 +11377,7 @@
       <c r="N374" s="1"/>
       <c r="O374" s="1"/>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>7720301</v>
       </c>
@@ -11398,7 +11406,7 @@
       <c r="N375" s="1"/>
       <c r="O375" s="1"/>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>7760101</v>
       </c>
@@ -11427,7 +11435,7 @@
       <c r="N376" s="1"/>
       <c r="O376" s="1"/>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>7850101</v>
       </c>
@@ -11456,7 +11464,7 @@
       <c r="N377" s="1"/>
       <c r="O377" s="1"/>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>7850103</v>
       </c>
@@ -11485,7 +11493,7 @@
       <c r="N378" s="1"/>
       <c r="O378" s="1"/>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>139</v>
       </c>
@@ -11514,7 +11522,7 @@
       <c r="N379" s="1"/>
       <c r="O379" s="1"/>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>140</v>
       </c>
@@ -11543,7 +11551,7 @@
       <c r="N380" s="1"/>
       <c r="O380" s="1"/>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>7140114</v>
       </c>
@@ -11572,7 +11580,7 @@
       <c r="N381" s="1"/>
       <c r="O381" s="1"/>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>7140201</v>
       </c>
@@ -11601,7 +11609,7 @@
       <c r="N382" s="1"/>
       <c r="O382" s="1"/>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>7140202</v>
       </c>
@@ -11630,7 +11638,7 @@
       <c r="N383" s="1"/>
       <c r="O383" s="1"/>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>7140205</v>
       </c>
@@ -11659,7 +11667,7 @@
       <c r="N384" s="1"/>
       <c r="O384" s="1"/>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>7140206</v>
       </c>
@@ -11688,7 +11696,7 @@
       <c r="N385" s="1"/>
       <c r="O385" s="1"/>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>7140208</v>
       </c>
@@ -11717,7 +11725,7 @@
       <c r="N386" s="1"/>
       <c r="O386" s="1"/>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>7140209</v>
       </c>
@@ -11746,7 +11754,7 @@
       <c r="N387" s="1"/>
       <c r="O387" s="1"/>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>7140210</v>
       </c>
@@ -11775,7 +11783,7 @@
       <c r="N388" s="1"/>
       <c r="O388" s="1"/>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>7140211</v>
       </c>
@@ -11804,7 +11812,7 @@
       <c r="N389" s="1"/>
       <c r="O389" s="1"/>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>7140212</v>
       </c>
@@ -11833,7 +11841,7 @@
       <c r="N390" s="1"/>
       <c r="O390" s="1"/>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>7140213</v>
       </c>
@@ -11862,7 +11870,7 @@
       <c r="N391" s="1"/>
       <c r="O391" s="1"/>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>7140217</v>
       </c>
@@ -11891,7 +11899,7 @@
       <c r="N392" s="1"/>
       <c r="O392" s="1"/>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>7140218</v>
       </c>
@@ -11920,7 +11928,7 @@
       <c r="N393" s="1"/>
       <c r="O393" s="1"/>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>7140219</v>
       </c>
@@ -11949,7 +11957,7 @@
       <c r="N394" s="1"/>
       <c r="O394" s="1"/>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>7140231</v>
       </c>
@@ -11978,7 +11986,7 @@
       <c r="N395" s="1"/>
       <c r="O395" s="1"/>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>7140247</v>
       </c>
@@ -12007,7 +12015,7 @@
       <c r="N396" s="1"/>
       <c r="O396" s="1"/>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>7140249</v>
       </c>
@@ -12036,7 +12044,7 @@
       <c r="N397" s="1"/>
       <c r="O397" s="1"/>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>7220201</v>
       </c>
@@ -12065,7 +12073,7 @@
       <c r="N398" s="1"/>
       <c r="O398" s="1"/>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>7220204</v>
       </c>
@@ -12094,7 +12102,7 @@
       <c r="N399" s="1"/>
       <c r="O399" s="1"/>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>7229042</v>
       </c>
@@ -12123,7 +12131,7 @@
       <c r="N400" s="1"/>
       <c r="O400" s="1"/>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>7310101</v>
       </c>
@@ -12152,7 +12160,7 @@
       <c r="N401" s="1"/>
       <c r="O401" s="1"/>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>7310109</v>
       </c>
@@ -12181,7 +12189,7 @@
       <c r="N402" s="1"/>
       <c r="O402" s="1"/>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>7310201</v>
       </c>
@@ -12210,7 +12218,7 @@
       <c r="N403" s="1"/>
       <c r="O403" s="1"/>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>7310205</v>
       </c>
@@ -12239,7 +12247,7 @@
       <c r="N404" s="1"/>
       <c r="O404" s="1"/>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>7310403</v>
       </c>
@@ -12268,7 +12276,7 @@
       <c r="N405" s="1"/>
       <c r="O405" s="1"/>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>7310601</v>
       </c>
@@ -12297,7 +12305,7 @@
       <c r="N406" s="1"/>
       <c r="O406" s="1"/>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>7310630</v>
       </c>
@@ -12326,7 +12334,7 @@
       <c r="N407" s="1"/>
       <c r="O407" s="1"/>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>7340101</v>
       </c>
@@ -12355,7 +12363,7 @@
       <c r="N408" s="1"/>
       <c r="O408" s="1"/>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>7340122</v>
       </c>
@@ -12384,7 +12392,7 @@
       <c r="N409" s="1"/>
       <c r="O409" s="1"/>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>7340201</v>
       </c>
@@ -12413,7 +12421,7 @@
       <c r="N410" s="1"/>
       <c r="O410" s="1"/>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>7340205</v>
       </c>
@@ -12442,7 +12450,7 @@
       <c r="N411" s="1"/>
       <c r="O411" s="1"/>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>7340301</v>
       </c>
@@ -12471,7 +12479,7 @@
       <c r="N412" s="1"/>
       <c r="O412" s="1"/>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>7380101</v>
       </c>
@@ -12500,7 +12508,7 @@
       <c r="N413" s="1"/>
       <c r="O413" s="1"/>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>7380102</v>
       </c>
@@ -12529,7 +12537,7 @@
       <c r="N414" s="1"/>
       <c r="O414" s="1"/>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>7380103</v>
       </c>
@@ -12558,7 +12566,7 @@
       <c r="N415" s="1"/>
       <c r="O415" s="1"/>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>7380107</v>
       </c>
@@ -12587,7 +12595,7 @@
       <c r="N416" s="1"/>
       <c r="O416" s="1"/>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>7420201</v>
       </c>
@@ -12616,7 +12624,7 @@
       <c r="N417" s="1"/>
       <c r="O417" s="1"/>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>7480101</v>
       </c>
@@ -12645,7 +12653,7 @@
       <c r="N418" s="1"/>
       <c r="O418" s="1"/>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>7480201</v>
       </c>
@@ -12674,7 +12682,7 @@
       <c r="N419" s="1"/>
       <c r="O419" s="1"/>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>7510205</v>
       </c>
@@ -12703,7 +12711,7 @@
       <c r="N420" s="1"/>
       <c r="O420" s="1"/>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>7510206</v>
       </c>
@@ -12732,7 +12740,7 @@
       <c r="N421" s="1"/>
       <c r="O421" s="1"/>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>7510301</v>
       </c>
@@ -12761,7 +12769,7 @@
       <c r="N422" s="1"/>
       <c r="O422" s="1"/>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>7510302</v>
       </c>
@@ -12790,7 +12798,7 @@
       <c r="N423" s="1"/>
       <c r="O423" s="1"/>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>7510303</v>
       </c>
@@ -12819,7 +12827,7 @@
       <c r="N424" s="1"/>
       <c r="O424" s="1"/>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>7520207</v>
       </c>
@@ -12848,7 +12856,7 @@
       <c r="N425" s="1"/>
       <c r="O425" s="1"/>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>7520216</v>
       </c>
@@ -12877,7 +12885,7 @@
       <c r="N426" s="1"/>
       <c r="O426" s="1"/>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>7540101</v>
       </c>
@@ -12906,7 +12914,7 @@
       <c r="N427" s="1"/>
       <c r="O427" s="1"/>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <v>7580101</v>
       </c>
@@ -12935,7 +12943,7 @@
       <c r="N428" s="1"/>
       <c r="O428" s="1"/>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>7580101</v>
       </c>
@@ -12964,7 +12972,7 @@
       <c r="N429" s="1"/>
       <c r="O429" s="1"/>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>7580201</v>
       </c>
@@ -12993,7 +13001,7 @@
       <c r="N430" s="1"/>
       <c r="O430" s="1"/>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>7580205</v>
       </c>
@@ -13022,7 +13030,7 @@
       <c r="N431" s="1"/>
       <c r="O431" s="1"/>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
         <v>7580301</v>
       </c>
@@ -13051,7 +13059,7 @@
       <c r="N432" s="1"/>
       <c r="O432" s="1"/>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
         <v>7620105</v>
       </c>
@@ -13080,7 +13088,7 @@
       <c r="N433" s="1"/>
       <c r="O433" s="1"/>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
         <v>7620109</v>
       </c>
@@ -13109,7 +13117,7 @@
       <c r="N434" s="1"/>
       <c r="O434" s="1"/>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
         <v>7620110</v>
       </c>
@@ -13138,7 +13146,7 @@
       <c r="N435" s="1"/>
       <c r="O435" s="1"/>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>7620301</v>
       </c>
@@ -13167,7 +13175,7 @@
       <c r="N436" s="1"/>
       <c r="O436" s="1"/>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <v>7640101</v>
       </c>
@@ -13196,7 +13204,7 @@
       <c r="N437" s="1"/>
       <c r="O437" s="1"/>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <v>7720301</v>
       </c>
@@ -13225,7 +13233,7 @@
       <c r="N438" s="1"/>
       <c r="O438" s="1"/>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <v>7760101</v>
       </c>
@@ -13254,7 +13262,7 @@
       <c r="N439" s="1"/>
       <c r="O439" s="1"/>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>7850101</v>
       </c>
@@ -13283,7 +13291,7 @@
       <c r="N440" s="1"/>
       <c r="O440" s="1"/>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>7850103</v>
       </c>
@@ -13312,7 +13320,7 @@
       <c r="N441" s="1"/>
       <c r="O441" s="1"/>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>137</v>
       </c>
@@ -13341,7 +13349,7 @@
       <c r="N442" s="1"/>
       <c r="O442" s="1"/>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>138</v>
       </c>
@@ -13370,7 +13378,7 @@
       <c r="N443" s="1"/>
       <c r="O443" s="1"/>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>139</v>
       </c>
@@ -13399,7 +13407,7 @@
       <c r="N444" s="1"/>
       <c r="O444" s="1"/>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>140</v>
       </c>
@@ -13428,7 +13436,7 @@
       <c r="N445" s="1"/>
       <c r="O445" s="1"/>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>7140114</v>
       </c>
@@ -13457,7 +13465,7 @@
       <c r="N446" s="1"/>
       <c r="O446" s="1"/>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <v>7140201</v>
       </c>
@@ -13486,7 +13494,7 @@
       <c r="N447" s="1"/>
       <c r="O447" s="1"/>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <v>7140202</v>
       </c>
@@ -13515,7 +13523,7 @@
       <c r="N448" s="1"/>
       <c r="O448" s="1"/>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>7140205</v>
       </c>
@@ -13544,7 +13552,7 @@
       <c r="N449" s="1"/>
       <c r="O449" s="1"/>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>7140206</v>
       </c>
@@ -13573,7 +13581,7 @@
       <c r="N450" s="1"/>
       <c r="O450" s="1"/>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>7140208</v>
       </c>
@@ -13602,7 +13610,7 @@
       <c r="N451" s="1"/>
       <c r="O451" s="1"/>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>7140209</v>
       </c>
@@ -13631,7 +13639,7 @@
       <c r="N452" s="1"/>
       <c r="O452" s="1"/>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>7140210</v>
       </c>
@@ -13660,7 +13668,7 @@
       <c r="N453" s="1"/>
       <c r="O453" s="1"/>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>7140211</v>
       </c>
@@ -13689,7 +13697,7 @@
       <c r="N454" s="1"/>
       <c r="O454" s="1"/>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>7140212</v>
       </c>
@@ -13718,7 +13726,7 @@
       <c r="N455" s="1"/>
       <c r="O455" s="1"/>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>7140213</v>
       </c>
@@ -13747,7 +13755,7 @@
       <c r="N456" s="1"/>
       <c r="O456" s="1"/>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <v>7140217</v>
       </c>
@@ -13776,7 +13784,7 @@
       <c r="N457" s="1"/>
       <c r="O457" s="1"/>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
         <v>7140218</v>
       </c>
@@ -13805,7 +13813,7 @@
       <c r="N458" s="1"/>
       <c r="O458" s="1"/>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <v>7140219</v>
       </c>
@@ -13834,7 +13842,7 @@
       <c r="N459" s="1"/>
       <c r="O459" s="1"/>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <v>7140231</v>
       </c>
@@ -13863,7 +13871,7 @@
       <c r="N460" s="1"/>
       <c r="O460" s="1"/>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>7140247</v>
       </c>
@@ -13892,7 +13900,7 @@
       <c r="N461" s="1"/>
       <c r="O461" s="1"/>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>7140249</v>
       </c>
@@ -13921,7 +13929,7 @@
       <c r="N462" s="1"/>
       <c r="O462" s="1"/>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <v>7220201</v>
       </c>
@@ -13950,7 +13958,7 @@
       <c r="N463" s="1"/>
       <c r="O463" s="1"/>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <v>7220204</v>
       </c>
@@ -13979,7 +13987,7 @@
       <c r="N464" s="1"/>
       <c r="O464" s="1"/>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <v>7229042</v>
       </c>
@@ -14008,7 +14016,7 @@
       <c r="N465" s="1"/>
       <c r="O465" s="1"/>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>7310101</v>
       </c>
@@ -14037,7 +14045,7 @@
       <c r="N466" s="1"/>
       <c r="O466" s="1"/>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <v>7310109</v>
       </c>
@@ -14066,7 +14074,7 @@
       <c r="N467" s="1"/>
       <c r="O467" s="1"/>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <v>7310201</v>
       </c>
@@ -14095,7 +14103,7 @@
       <c r="N468" s="1"/>
       <c r="O468" s="1"/>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
         <v>7310205</v>
       </c>
@@ -14124,7 +14132,7 @@
       <c r="N469" s="1"/>
       <c r="O469" s="1"/>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <v>7310403</v>
       </c>
@@ -14153,7 +14161,7 @@
       <c r="N470" s="1"/>
       <c r="O470" s="1"/>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>7310601</v>
       </c>
@@ -14182,7 +14190,7 @@
       <c r="N471" s="1"/>
       <c r="O471" s="1"/>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <v>7310630</v>
       </c>
@@ -14211,7 +14219,7 @@
       <c r="N472" s="1"/>
       <c r="O472" s="1"/>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <v>7340101</v>
       </c>
@@ -14240,7 +14248,7 @@
       <c r="N473" s="1"/>
       <c r="O473" s="1"/>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <v>7340122</v>
       </c>
@@ -14269,7 +14277,7 @@
       <c r="N474" s="1"/>
       <c r="O474" s="1"/>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <v>7340201</v>
       </c>
@@ -14298,7 +14306,7 @@
       <c r="N475" s="1"/>
       <c r="O475" s="1"/>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>7340205</v>
       </c>
@@ -14327,7 +14335,7 @@
       <c r="N476" s="1"/>
       <c r="O476" s="1"/>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <v>7340301</v>
       </c>
@@ -14356,7 +14364,7 @@
       <c r="N477" s="1"/>
       <c r="O477" s="1"/>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
         <v>7380101</v>
       </c>
@@ -14385,7 +14393,7 @@
       <c r="N478" s="1"/>
       <c r="O478" s="1"/>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <v>7380102</v>
       </c>
@@ -14414,7 +14422,7 @@
       <c r="N479" s="1"/>
       <c r="O479" s="1"/>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>7380103</v>
       </c>
@@ -14443,7 +14451,7 @@
       <c r="N480" s="1"/>
       <c r="O480" s="1"/>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>7380107</v>
       </c>
@@ -14472,7 +14480,7 @@
       <c r="N481" s="1"/>
       <c r="O481" s="1"/>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>7420201</v>
       </c>
@@ -14501,7 +14509,7 @@
       <c r="N482" s="1"/>
       <c r="O482" s="1"/>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>7480101</v>
       </c>
@@ -14530,7 +14538,7 @@
       <c r="N483" s="1"/>
       <c r="O483" s="1"/>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <v>7480201</v>
       </c>
@@ -14559,7 +14567,7 @@
       <c r="N484" s="1"/>
       <c r="O484" s="1"/>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>7510205</v>
       </c>
@@ -14588,7 +14596,7 @@
       <c r="N485" s="1"/>
       <c r="O485" s="1"/>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <v>7510206</v>
       </c>
@@ -14617,7 +14625,7 @@
       <c r="N486" s="1"/>
       <c r="O486" s="1"/>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>7510301</v>
       </c>
@@ -14646,7 +14654,7 @@
       <c r="N487" s="1"/>
       <c r="O487" s="1"/>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>7510302</v>
       </c>
@@ -14675,7 +14683,7 @@
       <c r="N488" s="1"/>
       <c r="O488" s="1"/>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <v>7510303</v>
       </c>
@@ -14704,7 +14712,7 @@
       <c r="N489" s="1"/>
       <c r="O489" s="1"/>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <v>7520207</v>
       </c>
@@ -14733,7 +14741,7 @@
       <c r="N490" s="1"/>
       <c r="O490" s="1"/>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <v>7520216</v>
       </c>
@@ -14762,7 +14770,7 @@
       <c r="N491" s="1"/>
       <c r="O491" s="1"/>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>7540101</v>
       </c>
@@ -14791,7 +14799,7 @@
       <c r="N492" s="1"/>
       <c r="O492" s="1"/>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <v>7580101</v>
       </c>
@@ -14820,7 +14828,7 @@
       <c r="N493" s="1"/>
       <c r="O493" s="1"/>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <v>7580101</v>
       </c>
@@ -14849,7 +14857,7 @@
       <c r="N494" s="1"/>
       <c r="O494" s="1"/>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <v>7580201</v>
       </c>
@@ -14878,7 +14886,7 @@
       <c r="N495" s="1"/>
       <c r="O495" s="1"/>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <v>7580205</v>
       </c>
@@ -14907,7 +14915,7 @@
       <c r="N496" s="1"/>
       <c r="O496" s="1"/>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <v>7580301</v>
       </c>
@@ -14936,7 +14944,7 @@
       <c r="N497" s="1"/>
       <c r="O497" s="1"/>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <v>7620105</v>
       </c>
@@ -14965,7 +14973,7 @@
       <c r="N498" s="1"/>
       <c r="O498" s="1"/>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <v>7620109</v>
       </c>
@@ -14994,7 +15002,7 @@
       <c r="N499" s="1"/>
       <c r="O499" s="1"/>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <v>7620110</v>
       </c>
@@ -15023,7 +15031,7 @@
       <c r="N500" s="1"/>
       <c r="O500" s="1"/>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <v>7620301</v>
       </c>
@@ -15052,7 +15060,7 @@
       <c r="N501" s="1"/>
       <c r="O501" s="1"/>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <v>7640101</v>
       </c>
@@ -15081,7 +15089,7 @@
       <c r="N502" s="1"/>
       <c r="O502" s="1"/>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
         <v>7720301</v>
       </c>
@@ -15110,7 +15118,7 @@
       <c r="N503" s="1"/>
       <c r="O503" s="1"/>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <v>7760101</v>
       </c>
@@ -15139,7 +15147,7 @@
       <c r="N504" s="1"/>
       <c r="O504" s="1"/>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>7850101</v>
       </c>
@@ -15168,7 +15176,7 @@
       <c r="N505" s="1"/>
       <c r="O505" s="1"/>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <v>7850103</v>
       </c>
@@ -15197,7 +15205,7 @@
       <c r="N506" s="1"/>
       <c r="O506" s="1"/>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>137</v>
       </c>
@@ -15226,7 +15234,7 @@
       <c r="N507" s="1"/>
       <c r="O507" s="1"/>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>138</v>
       </c>
@@ -15255,7 +15263,7 @@
       <c r="N508" s="1"/>
       <c r="O508" s="1"/>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>139</v>
       </c>
@@ -15284,7 +15292,7 @@
       <c r="N509" s="1"/>
       <c r="O509" s="1"/>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>140</v>
       </c>
@@ -15314,7 +15322,7 @@
       <c r="O510" s="1"/>
     </row>
     <row r="511" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A511" s="1">
+      <c r="A511" s="4">
         <v>7140114</v>
       </c>
       <c r="B511" s="1" t="s">
@@ -15343,7 +15351,7 @@
       </c>
     </row>
     <row r="512" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A512" s="1">
+      <c r="A512" s="4">
         <v>7140114</v>
       </c>
       <c r="B512" s="1" t="s">
@@ -15372,7 +15380,7 @@
       </c>
     </row>
     <row r="513" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A513" s="1">
+      <c r="A513" s="4">
         <v>7140202</v>
       </c>
       <c r="B513" s="1" t="s">
@@ -15401,7 +15409,7 @@
       </c>
     </row>
     <row r="514" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A514" s="1">
+      <c r="A514" s="4">
         <v>7140202</v>
       </c>
       <c r="B514" s="1" t="s">
@@ -15430,7 +15438,7 @@
       </c>
     </row>
     <row r="515" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A515" s="1">
+      <c r="A515" s="4">
         <v>7140205</v>
       </c>
       <c r="B515" s="1" t="s">
@@ -15459,7 +15467,7 @@
       </c>
     </row>
     <row r="516" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A516" s="1">
+      <c r="A516" s="4">
         <v>7140205</v>
       </c>
       <c r="B516" s="1" t="s">
@@ -15488,7 +15496,7 @@
       </c>
     </row>
     <row r="517" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A517" s="1">
+      <c r="A517" s="4">
         <v>7140208</v>
       </c>
       <c r="B517" s="1" t="s">
@@ -15517,7 +15525,7 @@
       </c>
     </row>
     <row r="518" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A518" s="1">
+      <c r="A518" s="4">
         <v>7140208</v>
       </c>
       <c r="B518" s="1" t="s">
@@ -15546,7 +15554,7 @@
       </c>
     </row>
     <row r="519" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A519" s="1">
+      <c r="A519" s="4">
         <v>7140209</v>
       </c>
       <c r="B519" s="1" t="s">
@@ -15575,7 +15583,7 @@
       </c>
     </row>
     <row r="520" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A520" s="1">
+      <c r="A520" s="4">
         <v>7140209</v>
       </c>
       <c r="B520" s="1" t="s">
@@ -15604,7 +15612,7 @@
       </c>
     </row>
     <row r="521" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A521" s="1">
+      <c r="A521" s="4">
         <v>7140210</v>
       </c>
       <c r="B521" s="1" t="s">
@@ -15633,7 +15641,7 @@
       </c>
     </row>
     <row r="522" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A522" s="1">
+      <c r="A522" s="4">
         <v>7140210</v>
       </c>
       <c r="B522" s="1" t="s">
@@ -15662,7 +15670,7 @@
       </c>
     </row>
     <row r="523" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A523" s="1">
+      <c r="A523" s="4">
         <v>7140211</v>
       </c>
       <c r="B523" s="1" t="s">
@@ -15691,7 +15699,7 @@
       </c>
     </row>
     <row r="524" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A524" s="1">
+      <c r="A524" s="4">
         <v>7140211</v>
       </c>
       <c r="B524" s="1" t="s">
@@ -15720,7 +15728,7 @@
       </c>
     </row>
     <row r="525" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A525" s="1">
+      <c r="A525" s="4">
         <v>7140212</v>
       </c>
       <c r="B525" s="1" t="s">
@@ -15749,7 +15757,7 @@
       </c>
     </row>
     <row r="526" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A526" s="1">
+      <c r="A526" s="4">
         <v>7140212</v>
       </c>
       <c r="B526" s="1" t="s">
@@ -15778,7 +15786,7 @@
       </c>
     </row>
     <row r="527" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A527" s="1">
+      <c r="A527" s="4">
         <v>7140213</v>
       </c>
       <c r="B527" s="1" t="s">
@@ -15807,7 +15815,7 @@
       </c>
     </row>
     <row r="528" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A528" s="1">
+      <c r="A528" s="4">
         <v>7140213</v>
       </c>
       <c r="B528" s="1" t="s">
@@ -15836,7 +15844,7 @@
       </c>
     </row>
     <row r="529" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A529" s="1">
+      <c r="A529" s="4">
         <v>7140217</v>
       </c>
       <c r="B529" s="1" t="s">
@@ -15865,7 +15873,7 @@
       </c>
     </row>
     <row r="530" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A530" s="1">
+      <c r="A530" s="4">
         <v>7140217</v>
       </c>
       <c r="B530" s="1" t="s">
@@ -15894,7 +15902,7 @@
       </c>
     </row>
     <row r="531" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A531" s="1">
+      <c r="A531" s="4">
         <v>7140218</v>
       </c>
       <c r="B531" s="1" t="s">
@@ -15923,7 +15931,7 @@
       </c>
     </row>
     <row r="532" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A532" s="1">
+      <c r="A532" s="4">
         <v>7140218</v>
       </c>
       <c r="B532" s="1" t="s">
@@ -15952,7 +15960,7 @@
       </c>
     </row>
     <row r="533" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A533" s="1">
+      <c r="A533" s="4">
         <v>7140219</v>
       </c>
       <c r="B533" s="1" t="s">
@@ -15981,7 +15989,7 @@
       </c>
     </row>
     <row r="534" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A534" s="1">
+      <c r="A534" s="4">
         <v>7140219</v>
       </c>
       <c r="B534" s="1" t="s">
@@ -16010,7 +16018,7 @@
       </c>
     </row>
     <row r="535" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A535" s="1">
+      <c r="A535" s="4">
         <v>7140231</v>
       </c>
       <c r="B535" s="1" t="s">
@@ -16043,7 +16051,7 @@
       </c>
     </row>
     <row r="536" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A536" s="1">
+      <c r="A536" s="4">
         <v>7140231</v>
       </c>
       <c r="B536" s="1" t="s">
@@ -16076,7 +16084,7 @@
       </c>
     </row>
     <row r="537" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A537" s="1">
+      <c r="A537" s="4">
         <v>7140247</v>
       </c>
       <c r="B537" s="1" t="s">
@@ -16105,7 +16113,7 @@
       </c>
     </row>
     <row r="538" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A538" s="1">
+      <c r="A538" s="4">
         <v>7140247</v>
       </c>
       <c r="B538" s="1" t="s">
@@ -16134,7 +16142,7 @@
       </c>
     </row>
     <row r="539" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A539" s="1">
+      <c r="A539" s="4">
         <v>7140249</v>
       </c>
       <c r="B539" s="1" t="s">
@@ -16163,7 +16171,7 @@
       </c>
     </row>
     <row r="540" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A540" s="1">
+      <c r="A540" s="4">
         <v>7140249</v>
       </c>
       <c r="B540" s="1" t="s">
@@ -16192,7 +16200,7 @@
       </c>
     </row>
     <row r="541" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A541" s="1">
+      <c r="A541" s="4">
         <v>7220201</v>
       </c>
       <c r="B541" s="1" t="s">
@@ -16225,7 +16233,7 @@
       </c>
     </row>
     <row r="542" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A542" s="1">
+      <c r="A542" s="4">
         <v>7220201</v>
       </c>
       <c r="B542" s="1" t="s">
@@ -16258,7 +16266,7 @@
       </c>
     </row>
     <row r="543" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A543" s="1">
+      <c r="A543" s="4">
         <v>7220204</v>
       </c>
       <c r="B543" s="1" t="s">
@@ -16291,7 +16299,7 @@
       </c>
     </row>
     <row r="544" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A544" s="1">
+      <c r="A544" s="4">
         <v>7220204</v>
       </c>
       <c r="B544" s="1" t="s">
@@ -16324,7 +16332,7 @@
       </c>
     </row>
     <row r="545" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A545" s="1">
+      <c r="A545" s="4">
         <v>7229042</v>
       </c>
       <c r="B545" s="1" t="s">
@@ -16353,7 +16361,7 @@
       </c>
     </row>
     <row r="546" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A546" s="1">
+      <c r="A546" s="4">
         <v>7229042</v>
       </c>
       <c r="B546" s="1" t="s">
@@ -16382,7 +16390,7 @@
       </c>
     </row>
     <row r="547" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A547" s="1">
+      <c r="A547" s="4">
         <v>7310101</v>
       </c>
       <c r="B547" s="1" t="s">
@@ -16411,7 +16419,7 @@
       </c>
     </row>
     <row r="548" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A548" s="1">
+      <c r="A548" s="4">
         <v>7310101</v>
       </c>
       <c r="B548" s="1" t="s">
@@ -16440,7 +16448,7 @@
       </c>
     </row>
     <row r="549" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A549" s="1">
+      <c r="A549" s="4">
         <v>7310104</v>
       </c>
       <c r="B549" s="1" t="s">
@@ -16469,7 +16477,7 @@
       </c>
     </row>
     <row r="550" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A550" s="1">
+      <c r="A550" s="4">
         <v>7310104</v>
       </c>
       <c r="B550" s="1" t="s">
@@ -16498,7 +16506,7 @@
       </c>
     </row>
     <row r="551" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A551" s="1">
+      <c r="A551" s="4">
         <v>7310109</v>
       </c>
       <c r="B551" s="1" t="s">
@@ -16527,7 +16535,7 @@
       </c>
     </row>
     <row r="552" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A552" s="1">
+      <c r="A552" s="4">
         <v>7310109</v>
       </c>
       <c r="B552" s="1" t="s">
@@ -16556,7 +16564,7 @@
       </c>
     </row>
     <row r="553" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A553" s="1">
+      <c r="A553" s="4">
         <v>7310110</v>
       </c>
       <c r="B553" s="1" t="s">
@@ -16585,7 +16593,7 @@
       </c>
     </row>
     <row r="554" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A554" s="1">
+      <c r="A554" s="4">
         <v>7310110</v>
       </c>
       <c r="B554" s="1" t="s">
@@ -16614,7 +16622,7 @@
       </c>
     </row>
     <row r="555" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A555" s="1">
+      <c r="A555" s="4">
         <v>7310201</v>
       </c>
       <c r="B555" s="1" t="s">
@@ -16643,7 +16651,7 @@
       </c>
     </row>
     <row r="556" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A556" s="1">
+      <c r="A556" s="4">
         <v>7310201</v>
       </c>
       <c r="B556" s="1" t="s">
@@ -16672,7 +16680,7 @@
       </c>
     </row>
     <row r="557" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A557" s="1">
+      <c r="A557" s="4">
         <v>7310205</v>
       </c>
       <c r="B557" s="1" t="s">
@@ -16701,7 +16709,7 @@
       </c>
     </row>
     <row r="558" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A558" s="1">
+      <c r="A558" s="4">
         <v>7310205</v>
       </c>
       <c r="B558" s="1" t="s">
@@ -16730,7 +16738,7 @@
       </c>
     </row>
     <row r="559" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A559" s="1">
+      <c r="A559" s="4">
         <v>7310403</v>
       </c>
       <c r="B559" s="1" t="s">
@@ -16759,7 +16767,7 @@
       </c>
     </row>
     <row r="560" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A560" s="1">
+      <c r="A560" s="4">
         <v>7310403</v>
       </c>
       <c r="B560" s="1" t="s">
@@ -16788,7 +16796,7 @@
       </c>
     </row>
     <row r="561" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A561" s="1">
+      <c r="A561" s="4">
         <v>7310601</v>
       </c>
       <c r="B561" s="1" t="s">
@@ -16817,7 +16825,7 @@
       </c>
     </row>
     <row r="562" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A562" s="1">
+      <c r="A562" s="4">
         <v>7310601</v>
       </c>
       <c r="B562" s="1" t="s">
@@ -16846,7 +16854,7 @@
       </c>
     </row>
     <row r="563" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A563" s="1">
+      <c r="A563" s="4">
         <v>7310630</v>
       </c>
       <c r="B563" s="1" t="s">
@@ -16875,7 +16883,7 @@
       </c>
     </row>
     <row r="564" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A564" s="1">
+      <c r="A564" s="4">
         <v>7310630</v>
       </c>
       <c r="B564" s="1" t="s">
@@ -16904,7 +16912,7 @@
       </c>
     </row>
     <row r="565" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A565" s="1">
+      <c r="A565" s="4">
         <v>7340101</v>
       </c>
       <c r="B565" s="1" t="s">
@@ -16933,7 +16941,7 @@
       </c>
     </row>
     <row r="566" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A566" s="1">
+      <c r="A566" s="4">
         <v>7340101</v>
       </c>
       <c r="B566" s="1" t="s">
@@ -16962,7 +16970,7 @@
       </c>
     </row>
     <row r="567" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A567" s="1">
+      <c r="A567" s="4">
         <v>7340115</v>
       </c>
       <c r="B567" s="1" t="s">
@@ -16991,7 +16999,7 @@
       </c>
     </row>
     <row r="568" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A568" s="1">
+      <c r="A568" s="4">
         <v>7340115</v>
       </c>
       <c r="B568" s="1" t="s">
@@ -17020,7 +17028,7 @@
       </c>
     </row>
     <row r="569" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A569" s="1">
+      <c r="A569" s="4">
         <v>7340122</v>
       </c>
       <c r="B569" s="1" t="s">
@@ -17049,7 +17057,7 @@
       </c>
     </row>
     <row r="570" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A570" s="1">
+      <c r="A570" s="4">
         <v>7340122</v>
       </c>
       <c r="B570" s="1" t="s">
@@ -17078,7 +17086,7 @@
       </c>
     </row>
     <row r="571" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A571" s="1">
+      <c r="A571" s="4">
         <v>7340201</v>
       </c>
       <c r="B571" s="1" t="s">
@@ -17107,7 +17115,7 @@
       </c>
     </row>
     <row r="572" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A572" s="1">
+      <c r="A572" s="4">
         <v>7340201</v>
       </c>
       <c r="B572" s="1" t="s">
@@ -17136,7 +17144,7 @@
       </c>
     </row>
     <row r="573" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A573" s="1">
+      <c r="A573" s="4">
         <v>7340205</v>
       </c>
       <c r="B573" s="1" t="s">
@@ -17165,7 +17173,7 @@
       </c>
     </row>
     <row r="574" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A574" s="1">
+      <c r="A574" s="4">
         <v>7340205</v>
       </c>
       <c r="B574" s="1" t="s">
@@ -17194,7 +17202,7 @@
       </c>
     </row>
     <row r="575" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A575" s="1">
+      <c r="A575" s="4">
         <v>7340301</v>
       </c>
       <c r="B575" s="1" t="s">
@@ -17223,7 +17231,7 @@
       </c>
     </row>
     <row r="576" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A576" s="1">
+      <c r="A576" s="4">
         <v>7340301</v>
       </c>
       <c r="B576" s="1" t="s">
@@ -17252,7 +17260,7 @@
       </c>
     </row>
     <row r="577" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A577" s="1">
+      <c r="A577" s="4">
         <v>7340302</v>
       </c>
       <c r="B577" s="1" t="s">
@@ -17281,7 +17289,7 @@
       </c>
     </row>
     <row r="578" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A578" s="1">
+      <c r="A578" s="4">
         <v>7340302</v>
       </c>
       <c r="B578" s="1" t="s">
@@ -17310,7 +17318,7 @@
       </c>
     </row>
     <row r="579" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A579" s="1">
+      <c r="A579" s="4">
         <v>7380101</v>
       </c>
       <c r="B579" s="1" t="s">
@@ -17339,7 +17347,7 @@
       </c>
     </row>
     <row r="580" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A580" s="1">
+      <c r="A580" s="4">
         <v>7380101</v>
       </c>
       <c r="B580" s="1" t="s">
@@ -17368,7 +17376,7 @@
       </c>
     </row>
     <row r="581" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A581" s="1">
+      <c r="A581" s="4">
         <v>7380102</v>
       </c>
       <c r="B581" s="1" t="s">
@@ -17397,7 +17405,7 @@
       </c>
     </row>
     <row r="582" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A582" s="1">
+      <c r="A582" s="4">
         <v>7380102</v>
       </c>
       <c r="B582" s="1" t="s">
@@ -17426,7 +17434,7 @@
       </c>
     </row>
     <row r="583" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A583" s="1">
+      <c r="A583" s="4">
         <v>7380103</v>
       </c>
       <c r="B583" s="1" t="s">
@@ -17455,7 +17463,7 @@
       </c>
     </row>
     <row r="584" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A584" s="1">
+      <c r="A584" s="4">
         <v>7380103</v>
       </c>
       <c r="B584" s="1" t="s">
@@ -17484,7 +17492,7 @@
       </c>
     </row>
     <row r="585" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A585" s="1">
+      <c r="A585" s="4">
         <v>7380107</v>
       </c>
       <c r="B585" s="1" t="s">
@@ -17513,7 +17521,7 @@
       </c>
     </row>
     <row r="586" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A586" s="1">
+      <c r="A586" s="4">
         <v>7380107</v>
       </c>
       <c r="B586" s="1" t="s">
@@ -17542,7 +17550,7 @@
       </c>
     </row>
     <row r="587" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A587" s="1">
+      <c r="A587" s="4">
         <v>7420201</v>
       </c>
       <c r="B587" s="1" t="s">
@@ -17571,7 +17579,7 @@
       </c>
     </row>
     <row r="588" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A588" s="1">
+      <c r="A588" s="4">
         <v>7420201</v>
       </c>
       <c r="B588" s="1" t="s">
@@ -17600,7 +17608,7 @@
       </c>
     </row>
     <row r="589" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A589" s="1">
+      <c r="A589" s="4">
         <v>7480101</v>
       </c>
       <c r="B589" s="1" t="s">
@@ -17629,7 +17637,7 @@
       </c>
     </row>
     <row r="590" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A590" s="1">
+      <c r="A590" s="4">
         <v>7480101</v>
       </c>
       <c r="B590" s="1" t="s">
@@ -17658,7 +17666,7 @@
       </c>
     </row>
     <row r="591" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A591" s="1">
+      <c r="A591" s="4">
         <v>7480201</v>
       </c>
       <c r="B591" s="1" t="s">
@@ -17687,7 +17695,7 @@
       </c>
     </row>
     <row r="592" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A592" s="1">
+      <c r="A592" s="4">
         <v>7480201</v>
       </c>
       <c r="B592" s="1" t="s">
@@ -17716,7 +17724,7 @@
       </c>
     </row>
     <row r="593" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A593" s="1">
+      <c r="A593" s="4">
         <v>7510205</v>
       </c>
       <c r="B593" s="1" t="s">
@@ -17745,7 +17753,7 @@
       </c>
     </row>
     <row r="594" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A594" s="1">
+      <c r="A594" s="4">
         <v>7510205</v>
       </c>
       <c r="B594" s="1" t="s">
@@ -17774,7 +17782,7 @@
       </c>
     </row>
     <row r="595" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A595" s="1">
+      <c r="A595" s="4">
         <v>7510206</v>
       </c>
       <c r="B595" s="1" t="s">
@@ -17803,7 +17811,7 @@
       </c>
     </row>
     <row r="596" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A596" s="1">
+      <c r="A596" s="4">
         <v>7510206</v>
       </c>
       <c r="B596" s="1" t="s">
@@ -17832,7 +17840,7 @@
       </c>
     </row>
     <row r="597" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A597" s="1">
+      <c r="A597" s="4">
         <v>7510301</v>
       </c>
       <c r="B597" s="1" t="s">
@@ -17861,7 +17869,7 @@
       </c>
     </row>
     <row r="598" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A598" s="1">
+      <c r="A598" s="4">
         <v>7510301</v>
       </c>
       <c r="B598" s="1" t="s">
@@ -17890,7 +17898,7 @@
       </c>
     </row>
     <row r="599" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A599" s="1">
+      <c r="A599" s="4">
         <v>7510302</v>
       </c>
       <c r="B599" s="1" t="s">
@@ -17919,7 +17927,7 @@
       </c>
     </row>
     <row r="600" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A600" s="1">
+      <c r="A600" s="4">
         <v>7510302</v>
       </c>
       <c r="B600" s="1" t="s">
@@ -17948,7 +17956,7 @@
       </c>
     </row>
     <row r="601" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A601" s="1">
+      <c r="A601" s="4">
         <v>7510303</v>
       </c>
       <c r="B601" s="1" t="s">
@@ -17977,7 +17985,7 @@
       </c>
     </row>
     <row r="602" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A602" s="1">
+      <c r="A602" s="4">
         <v>7510303</v>
       </c>
       <c r="B602" s="1" t="s">
@@ -18006,7 +18014,7 @@
       </c>
     </row>
     <row r="603" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A603" s="1">
+      <c r="A603" s="4">
         <v>7520207</v>
       </c>
       <c r="B603" s="1" t="s">
@@ -18035,7 +18043,7 @@
       </c>
     </row>
     <row r="604" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A604" s="1">
+      <c r="A604" s="4">
         <v>7520207</v>
       </c>
       <c r="B604" s="1" t="s">
@@ -18064,7 +18072,7 @@
       </c>
     </row>
     <row r="605" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A605" s="1">
+      <c r="A605" s="4">
         <v>7520216</v>
       </c>
       <c r="B605" s="1" t="s">
@@ -18093,7 +18101,7 @@
       </c>
     </row>
     <row r="606" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A606" s="1">
+      <c r="A606" s="4">
         <v>7520216</v>
       </c>
       <c r="B606" s="1" t="s">
@@ -18122,7 +18130,7 @@
       </c>
     </row>
     <row r="607" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A607" s="1">
+      <c r="A607" s="4">
         <v>7540101</v>
       </c>
       <c r="B607" s="1" t="s">
@@ -18151,7 +18159,7 @@
       </c>
     </row>
     <row r="608" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A608" s="1">
+      <c r="A608" s="4">
         <v>7540101</v>
       </c>
       <c r="B608" s="1" t="s">
@@ -18180,7 +18188,7 @@
       </c>
     </row>
     <row r="609" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A609" s="1">
+      <c r="A609" s="4">
         <v>7580101</v>
       </c>
       <c r="B609" s="1" t="s">
@@ -18211,7 +18219,7 @@
       </c>
     </row>
     <row r="610" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A610" s="1">
+      <c r="A610" s="4">
         <v>7580101</v>
       </c>
       <c r="B610" s="1" t="s">
@@ -18242,7 +18250,7 @@
       </c>
     </row>
     <row r="611" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A611" s="1">
+      <c r="A611" s="4">
         <v>7580201</v>
       </c>
       <c r="B611" s="1" t="s">
@@ -18271,7 +18279,7 @@
       </c>
     </row>
     <row r="612" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A612" s="1">
+      <c r="A612" s="4">
         <v>7580201</v>
       </c>
       <c r="B612" s="1" t="s">
@@ -18300,7 +18308,7 @@
       </c>
     </row>
     <row r="613" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A613" s="1">
+      <c r="A613" s="4">
         <v>7580205</v>
       </c>
       <c r="B613" s="1" t="s">
@@ -18329,7 +18337,7 @@
       </c>
     </row>
     <row r="614" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A614" s="1">
+      <c r="A614" s="4">
         <v>7580205</v>
       </c>
       <c r="B614" s="1" t="s">
@@ -18358,7 +18366,7 @@
       </c>
     </row>
     <row r="615" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A615" s="1">
+      <c r="A615" s="4">
         <v>7580301</v>
       </c>
       <c r="B615" s="1" t="s">
@@ -18387,7 +18395,7 @@
       </c>
     </row>
     <row r="616" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A616" s="1">
+      <c r="A616" s="4">
         <v>7580301</v>
       </c>
       <c r="B616" s="1" t="s">
@@ -18416,7 +18424,7 @@
       </c>
     </row>
     <row r="617" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A617" s="1">
+      <c r="A617" s="4">
         <v>7620105</v>
       </c>
       <c r="B617" s="1" t="s">
@@ -18445,7 +18453,7 @@
       </c>
     </row>
     <row r="618" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A618" s="1">
+      <c r="A618" s="4">
         <v>7620105</v>
       </c>
       <c r="B618" s="1" t="s">
@@ -18474,7 +18482,7 @@
       </c>
     </row>
     <row r="619" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A619" s="1">
+      <c r="A619" s="4">
         <v>7620109</v>
       </c>
       <c r="B619" s="1" t="s">
@@ -18503,7 +18511,7 @@
       </c>
     </row>
     <row r="620" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A620" s="1">
+      <c r="A620" s="4">
         <v>7620109</v>
       </c>
       <c r="B620" s="1" t="s">
@@ -18532,7 +18540,7 @@
       </c>
     </row>
     <row r="621" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A621" s="1">
+      <c r="A621" s="4">
         <v>7620110</v>
       </c>
       <c r="B621" s="1" t="s">
@@ -18561,7 +18569,7 @@
       </c>
     </row>
     <row r="622" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A622" s="1">
+      <c r="A622" s="4">
         <v>7620110</v>
       </c>
       <c r="B622" s="1" t="s">
@@ -18590,7 +18598,7 @@
       </c>
     </row>
     <row r="623" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A623" s="1">
+      <c r="A623" s="4">
         <v>7620301</v>
       </c>
       <c r="B623" s="1" t="s">
@@ -18619,7 +18627,7 @@
       </c>
     </row>
     <row r="624" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A624" s="1">
+      <c r="A624" s="4">
         <v>7620301</v>
       </c>
       <c r="B624" s="1" t="s">
@@ -18648,7 +18656,7 @@
       </c>
     </row>
     <row r="625" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A625" s="1">
+      <c r="A625" s="4">
         <v>7640101</v>
       </c>
       <c r="B625" s="1" t="s">
@@ -18677,7 +18685,7 @@
       </c>
     </row>
     <row r="626" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A626" s="1">
+      <c r="A626" s="4">
         <v>7640101</v>
       </c>
       <c r="B626" s="1" t="s">
@@ -18706,7 +18714,7 @@
       </c>
     </row>
     <row r="627" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A627" s="1">
+      <c r="A627" s="4">
         <v>7720301</v>
       </c>
       <c r="B627" s="1" t="s">
@@ -18735,7 +18743,7 @@
       </c>
     </row>
     <row r="628" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A628" s="1">
+      <c r="A628" s="4">
         <v>7720301</v>
       </c>
       <c r="B628" s="1" t="s">
@@ -18764,7 +18772,7 @@
       </c>
     </row>
     <row r="629" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A629" s="1">
+      <c r="A629" s="4">
         <v>7760101</v>
       </c>
       <c r="B629" s="1" t="s">
@@ -18793,7 +18801,7 @@
       </c>
     </row>
     <row r="630" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A630" s="1">
+      <c r="A630" s="4">
         <v>7760101</v>
       </c>
       <c r="B630" s="1" t="s">
@@ -18822,7 +18830,7 @@
       </c>
     </row>
     <row r="631" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A631" s="1">
+      <c r="A631" s="4">
         <v>7850101</v>
       </c>
       <c r="B631" s="1" t="s">
@@ -18851,7 +18859,7 @@
       </c>
     </row>
     <row r="632" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A632" s="1">
+      <c r="A632" s="4">
         <v>7850101</v>
       </c>
       <c r="B632" s="1" t="s">
@@ -18880,7 +18888,7 @@
       </c>
     </row>
     <row r="633" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A633" s="1">
+      <c r="A633" s="4">
         <v>7850103</v>
       </c>
       <c r="B633" s="1" t="s">
@@ -18909,7 +18917,7 @@
       </c>
     </row>
     <row r="634" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A634" s="1">
+      <c r="A634" s="4">
         <v>7850103</v>
       </c>
       <c r="B634" s="1" t="s">
@@ -18938,7 +18946,7 @@
       </c>
     </row>
     <row r="635" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A635" s="1" t="s">
+      <c r="A635" s="4" t="s">
         <v>137</v>
       </c>
       <c r="B635" s="1" t="s">
@@ -18967,7 +18975,7 @@
       </c>
     </row>
     <row r="636" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A636" s="1" t="s">
+      <c r="A636" s="4" t="s">
         <v>137</v>
       </c>
       <c r="B636" s="1" t="s">
@@ -18996,7 +19004,7 @@
       </c>
     </row>
     <row r="637" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A637" s="1" t="s">
+      <c r="A637" s="4" t="s">
         <v>138</v>
       </c>
       <c r="B637" s="1" t="s">
@@ -19029,7 +19037,7 @@
       </c>
     </row>
     <row r="638" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A638" s="1" t="s">
+      <c r="A638" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B638" s="1" t="s">
@@ -19058,7 +19066,7 @@
       </c>
     </row>
     <row r="639" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A639" s="1" t="s">
+      <c r="A639" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B639" s="1" t="s">
@@ -19087,7 +19095,7 @@
       </c>
     </row>
     <row r="640" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A640" s="1" t="s">
+      <c r="A640" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B640" s="1" t="s">
@@ -19116,7 +19124,7 @@
       </c>
     </row>
     <row r="641" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A641" s="1" t="s">
+      <c r="A641" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B641" s="1" t="s">
@@ -19145,7 +19153,7 @@
       </c>
     </row>
     <row r="642" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A642" s="1">
+      <c r="A642" s="4">
         <v>7220201</v>
       </c>
       <c r="B642" s="1" t="s">
@@ -19184,7 +19192,7 @@
       </c>
     </row>
     <row r="643" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A643" s="1">
+      <c r="A643" s="4">
         <v>7220201</v>
       </c>
       <c r="B643" s="1" t="s">
@@ -19223,7 +19231,7 @@
       </c>
     </row>
     <row r="644" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A644" s="1">
+      <c r="A644" s="4">
         <v>7220204</v>
       </c>
       <c r="B644" s="1" t="s">
@@ -19262,7 +19270,7 @@
       </c>
     </row>
     <row r="645" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A645" s="1">
+      <c r="A645" s="4">
         <v>7220204</v>
       </c>
       <c r="B645" s="1" t="s">
@@ -19301,7 +19309,7 @@
       </c>
     </row>
     <row r="646" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A646" s="1">
+      <c r="A646" s="4">
         <v>7229042</v>
       </c>
       <c r="B646" s="1" t="s">
@@ -19334,7 +19342,7 @@
       </c>
     </row>
     <row r="647" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A647" s="1">
+      <c r="A647" s="4">
         <v>7229042</v>
       </c>
       <c r="B647" s="1" t="s">
@@ -19367,7 +19375,7 @@
       </c>
     </row>
     <row r="648" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A648" s="1">
+      <c r="A648" s="4">
         <v>7310101</v>
       </c>
       <c r="B648" s="1" t="s">
@@ -19400,7 +19408,7 @@
       </c>
     </row>
     <row r="649" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A649" s="1">
+      <c r="A649" s="4">
         <v>7310101</v>
       </c>
       <c r="B649" s="1" t="s">
@@ -19433,7 +19441,7 @@
       </c>
     </row>
     <row r="650" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A650" s="1">
+      <c r="A650" s="4">
         <v>7310104</v>
       </c>
       <c r="B650" s="1" t="s">
@@ -19466,7 +19474,7 @@
       </c>
     </row>
     <row r="651" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A651" s="1">
+      <c r="A651" s="4">
         <v>7310104</v>
       </c>
       <c r="B651" s="1" t="s">
@@ -19499,7 +19507,7 @@
       </c>
     </row>
     <row r="652" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A652" s="1">
+      <c r="A652" s="4">
         <v>7310109</v>
       </c>
       <c r="B652" s="1" t="s">
@@ -19532,7 +19540,7 @@
       </c>
     </row>
     <row r="653" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A653" s="1">
+      <c r="A653" s="4">
         <v>7310109</v>
       </c>
       <c r="B653" s="1" t="s">
@@ -19565,7 +19573,7 @@
       </c>
     </row>
     <row r="654" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A654" s="1">
+      <c r="A654" s="4">
         <v>7310110</v>
       </c>
       <c r="B654" s="1" t="s">
@@ -19598,7 +19606,7 @@
       </c>
     </row>
     <row r="655" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A655" s="1">
+      <c r="A655" s="4">
         <v>7310110</v>
       </c>
       <c r="B655" s="1" t="s">
@@ -19631,7 +19639,7 @@
       </c>
     </row>
     <row r="656" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A656" s="1">
+      <c r="A656" s="4">
         <v>7310201</v>
       </c>
       <c r="B656" s="1" t="s">
@@ -19664,7 +19672,7 @@
       </c>
     </row>
     <row r="657" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A657" s="1">
+      <c r="A657" s="4">
         <v>7310201</v>
       </c>
       <c r="B657" s="1" t="s">
@@ -19697,7 +19705,7 @@
       </c>
     </row>
     <row r="658" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A658" s="1">
+      <c r="A658" s="4">
         <v>7310205</v>
       </c>
       <c r="B658" s="1" t="s">
@@ -19730,7 +19738,7 @@
       </c>
     </row>
     <row r="659" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A659" s="1">
+      <c r="A659" s="4">
         <v>7310205</v>
       </c>
       <c r="B659" s="1" t="s">
@@ -19763,7 +19771,7 @@
       </c>
     </row>
     <row r="660" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A660" s="1">
+      <c r="A660" s="4">
         <v>7310601</v>
       </c>
       <c r="B660" s="1" t="s">
@@ -19796,7 +19804,7 @@
       </c>
     </row>
     <row r="661" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A661" s="1">
+      <c r="A661" s="4">
         <v>7310601</v>
       </c>
       <c r="B661" s="1" t="s">
@@ -19829,7 +19837,7 @@
       </c>
     </row>
     <row r="662" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A662" s="1">
+      <c r="A662" s="4">
         <v>7310630</v>
       </c>
       <c r="B662" s="1" t="s">
@@ -19862,7 +19870,7 @@
       </c>
     </row>
     <row r="663" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A663" s="1">
+      <c r="A663" s="4">
         <v>7310630</v>
       </c>
       <c r="B663" s="1" t="s">
@@ -19895,7 +19903,7 @@
       </c>
     </row>
     <row r="664" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A664" s="1">
+      <c r="A664" s="4">
         <v>7340101</v>
       </c>
       <c r="B664" s="1" t="s">
@@ -19928,7 +19936,7 @@
       </c>
     </row>
     <row r="665" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A665" s="1">
+      <c r="A665" s="4">
         <v>7340101</v>
       </c>
       <c r="B665" s="1" t="s">
@@ -19961,7 +19969,7 @@
       </c>
     </row>
     <row r="666" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A666" s="1">
+      <c r="A666" s="4">
         <v>7340115</v>
       </c>
       <c r="B666" s="1" t="s">
@@ -19994,7 +20002,7 @@
       </c>
     </row>
     <row r="667" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A667" s="1">
+      <c r="A667" s="4">
         <v>7340115</v>
       </c>
       <c r="B667" s="1" t="s">
@@ -20027,7 +20035,7 @@
       </c>
     </row>
     <row r="668" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A668" s="1">
+      <c r="A668" s="4">
         <v>7340122</v>
       </c>
       <c r="B668" s="1" t="s">
@@ -20060,7 +20068,7 @@
       </c>
     </row>
     <row r="669" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A669" s="1">
+      <c r="A669" s="4">
         <v>7340122</v>
       </c>
       <c r="B669" s="1" t="s">
@@ -20093,7 +20101,7 @@
       </c>
     </row>
     <row r="670" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A670" s="1">
+      <c r="A670" s="4">
         <v>7340201</v>
       </c>
       <c r="B670" s="1" t="s">
@@ -20126,7 +20134,7 @@
       </c>
     </row>
     <row r="671" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A671" s="1">
+      <c r="A671" s="4">
         <v>7340201</v>
       </c>
       <c r="B671" s="1" t="s">
@@ -20159,7 +20167,7 @@
       </c>
     </row>
     <row r="672" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A672" s="1">
+      <c r="A672" s="4">
         <v>7340205</v>
       </c>
       <c r="B672" s="1" t="s">
@@ -20192,7 +20200,7 @@
       </c>
     </row>
     <row r="673" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A673" s="1">
+      <c r="A673" s="4">
         <v>7340205</v>
       </c>
       <c r="B673" s="1" t="s">
@@ -20225,7 +20233,7 @@
       </c>
     </row>
     <row r="674" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A674" s="1">
+      <c r="A674" s="4">
         <v>7340301</v>
       </c>
       <c r="B674" s="1" t="s">
@@ -20258,7 +20266,7 @@
       </c>
     </row>
     <row r="675" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A675" s="1">
+      <c r="A675" s="4">
         <v>7340301</v>
       </c>
       <c r="B675" s="1" t="s">
@@ -20291,7 +20299,7 @@
       </c>
     </row>
     <row r="676" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A676" s="1">
+      <c r="A676" s="4">
         <v>7340302</v>
       </c>
       <c r="B676" s="1" t="s">
@@ -20324,7 +20332,7 @@
       </c>
     </row>
     <row r="677" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A677" s="1">
+      <c r="A677" s="4">
         <v>7340302</v>
       </c>
       <c r="B677" s="1" t="s">
@@ -20357,7 +20365,7 @@
       </c>
     </row>
     <row r="678" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A678" s="1">
+      <c r="A678" s="4">
         <v>7380101</v>
       </c>
       <c r="B678" s="1" t="s">
@@ -20392,7 +20400,7 @@
       </c>
     </row>
     <row r="679" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A679" s="1">
+      <c r="A679" s="4">
         <v>7380101</v>
       </c>
       <c r="B679" s="1" t="s">
@@ -20427,7 +20435,7 @@
       </c>
     </row>
     <row r="680" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A680" s="1">
+      <c r="A680" s="4">
         <v>7380102</v>
       </c>
       <c r="B680" s="1" t="s">
@@ -20462,7 +20470,7 @@
       </c>
     </row>
     <row r="681" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A681" s="1">
+      <c r="A681" s="4">
         <v>7380102</v>
       </c>
       <c r="B681" s="1" t="s">
@@ -20497,7 +20505,7 @@
       </c>
     </row>
     <row r="682" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A682" s="1">
+      <c r="A682" s="4">
         <v>7380103</v>
       </c>
       <c r="B682" s="1" t="s">
@@ -20532,7 +20540,7 @@
       </c>
     </row>
     <row r="683" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A683" s="1">
+      <c r="A683" s="4">
         <v>7380103</v>
       </c>
       <c r="B683" s="1" t="s">
@@ -20567,7 +20575,7 @@
       </c>
     </row>
     <row r="684" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A684" s="1">
+      <c r="A684" s="4">
         <v>7380107</v>
       </c>
       <c r="B684" s="1" t="s">
@@ -20602,7 +20610,7 @@
       </c>
     </row>
     <row r="685" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A685" s="1">
+      <c r="A685" s="4">
         <v>7380107</v>
       </c>
       <c r="B685" s="1" t="s">
@@ -20637,7 +20645,7 @@
       </c>
     </row>
     <row r="686" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A686" s="1">
+      <c r="A686" s="4">
         <v>7420201</v>
       </c>
       <c r="B686" s="1" t="s">
@@ -20670,7 +20678,7 @@
       </c>
     </row>
     <row r="687" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A687" s="1">
+      <c r="A687" s="4">
         <v>7420201</v>
       </c>
       <c r="B687" s="1" t="s">
@@ -20703,7 +20711,7 @@
       </c>
     </row>
     <row r="688" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A688" s="1">
+      <c r="A688" s="4">
         <v>7480101</v>
       </c>
       <c r="B688" s="1" t="s">
@@ -20736,7 +20744,7 @@
       </c>
     </row>
     <row r="689" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A689" s="1">
+      <c r="A689" s="4">
         <v>7480101</v>
       </c>
       <c r="B689" s="1" t="s">
@@ -20769,7 +20777,7 @@
       </c>
     </row>
     <row r="690" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A690" s="1">
+      <c r="A690" s="4">
         <v>7480201</v>
       </c>
       <c r="B690" s="1" t="s">
@@ -20802,7 +20810,7 @@
       </c>
     </row>
     <row r="691" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A691" s="1">
+      <c r="A691" s="4">
         <v>7480201</v>
       </c>
       <c r="B691" s="1" t="s">
@@ -20835,7 +20843,7 @@
       </c>
     </row>
     <row r="692" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A692" s="1">
+      <c r="A692" s="4">
         <v>7510205</v>
       </c>
       <c r="B692" s="1" t="s">
@@ -20868,7 +20876,7 @@
       </c>
     </row>
     <row r="693" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A693" s="1">
+      <c r="A693" s="4">
         <v>7510205</v>
       </c>
       <c r="B693" s="1" t="s">
@@ -20901,7 +20909,7 @@
       </c>
     </row>
     <row r="694" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A694" s="1">
+      <c r="A694" s="4">
         <v>7510206</v>
       </c>
       <c r="B694" s="1" t="s">
@@ -20934,7 +20942,7 @@
       </c>
     </row>
     <row r="695" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A695" s="1">
+      <c r="A695" s="4">
         <v>7510206</v>
       </c>
       <c r="B695" s="1" t="s">
@@ -20967,7 +20975,7 @@
       </c>
     </row>
     <row r="696" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A696" s="1">
+      <c r="A696" s="4">
         <v>7510301</v>
       </c>
       <c r="B696" s="1" t="s">
@@ -21000,7 +21008,7 @@
       </c>
     </row>
     <row r="697" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A697" s="1">
+      <c r="A697" s="4">
         <v>7510301</v>
       </c>
       <c r="B697" s="1" t="s">
@@ -21033,7 +21041,7 @@
       </c>
     </row>
     <row r="698" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A698" s="1">
+      <c r="A698" s="4">
         <v>7510302</v>
       </c>
       <c r="B698" s="1" t="s">
@@ -21066,7 +21074,7 @@
       </c>
     </row>
     <row r="699" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A699" s="1">
+      <c r="A699" s="4">
         <v>7510302</v>
       </c>
       <c r="B699" s="1" t="s">
@@ -21099,7 +21107,7 @@
       </c>
     </row>
     <row r="700" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A700" s="1">
+      <c r="A700" s="4">
         <v>7510303</v>
       </c>
       <c r="B700" s="1" t="s">
@@ -21132,7 +21140,7 @@
       </c>
     </row>
     <row r="701" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A701" s="1">
+      <c r="A701" s="4">
         <v>7510303</v>
       </c>
       <c r="B701" s="1" t="s">
@@ -21165,7 +21173,7 @@
       </c>
     </row>
     <row r="702" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A702" s="1">
+      <c r="A702" s="4">
         <v>7520207</v>
       </c>
       <c r="B702" s="1" t="s">
@@ -21198,7 +21206,7 @@
       </c>
     </row>
     <row r="703" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A703" s="1">
+      <c r="A703" s="4">
         <v>7520207</v>
       </c>
       <c r="B703" s="1" t="s">
@@ -21231,7 +21239,7 @@
       </c>
     </row>
     <row r="704" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A704" s="1">
+      <c r="A704" s="4">
         <v>7520216</v>
       </c>
       <c r="B704" s="1" t="s">
@@ -21264,7 +21272,7 @@
       </c>
     </row>
     <row r="705" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A705" s="1">
+      <c r="A705" s="4">
         <v>7520216</v>
       </c>
       <c r="B705" s="1" t="s">
@@ -21297,7 +21305,7 @@
       </c>
     </row>
     <row r="706" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A706" s="1">
+      <c r="A706" s="4">
         <v>7540101</v>
       </c>
       <c r="B706" s="1" t="s">
@@ -21330,7 +21338,7 @@
       </c>
     </row>
     <row r="707" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A707" s="1">
+      <c r="A707" s="4">
         <v>7540101</v>
       </c>
       <c r="B707" s="1" t="s">
@@ -21363,7 +21371,7 @@
       </c>
     </row>
     <row r="708" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A708" s="1">
+      <c r="A708" s="4">
         <v>7580101</v>
       </c>
       <c r="B708" s="1" t="s">
@@ -21398,7 +21406,7 @@
       </c>
     </row>
     <row r="709" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A709" s="1">
+      <c r="A709" s="4">
         <v>7580101</v>
       </c>
       <c r="B709" s="1" t="s">
@@ -21433,7 +21441,7 @@
       </c>
     </row>
     <row r="710" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A710" s="1">
+      <c r="A710" s="4">
         <v>7580201</v>
       </c>
       <c r="B710" s="1" t="s">
@@ -21466,7 +21474,7 @@
       </c>
     </row>
     <row r="711" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A711" s="1">
+      <c r="A711" s="4">
         <v>7580201</v>
       </c>
       <c r="B711" s="1" t="s">
@@ -21499,7 +21507,7 @@
       </c>
     </row>
     <row r="712" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A712" s="1">
+      <c r="A712" s="4">
         <v>7580205</v>
       </c>
       <c r="B712" s="1" t="s">
@@ -21532,7 +21540,7 @@
       </c>
     </row>
     <row r="713" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A713" s="1">
+      <c r="A713" s="4">
         <v>7580205</v>
       </c>
       <c r="B713" s="1" t="s">
@@ -21565,7 +21573,7 @@
       </c>
     </row>
     <row r="714" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A714" s="1">
+      <c r="A714" s="4">
         <v>7580301</v>
       </c>
       <c r="B714" s="1" t="s">
@@ -21598,7 +21606,7 @@
       </c>
     </row>
     <row r="715" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A715" s="1">
+      <c r="A715" s="4">
         <v>7580301</v>
       </c>
       <c r="B715" s="1" t="s">
@@ -21631,7 +21639,7 @@
       </c>
     </row>
     <row r="716" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A716" s="1">
+      <c r="A716" s="4">
         <v>7620105</v>
       </c>
       <c r="B716" s="1" t="s">
@@ -21664,7 +21672,7 @@
       </c>
     </row>
     <row r="717" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A717" s="1">
+      <c r="A717" s="4">
         <v>7620105</v>
       </c>
       <c r="B717" s="1" t="s">
@@ -21697,7 +21705,7 @@
       </c>
     </row>
     <row r="718" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A718" s="1">
+      <c r="A718" s="4">
         <v>7620109</v>
       </c>
       <c r="B718" s="1" t="s">
@@ -21730,7 +21738,7 @@
       </c>
     </row>
     <row r="719" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A719" s="1">
+      <c r="A719" s="4">
         <v>7620109</v>
       </c>
       <c r="B719" s="1" t="s">
@@ -21763,7 +21771,7 @@
       </c>
     </row>
     <row r="720" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A720" s="1">
+      <c r="A720" s="4">
         <v>7620110</v>
       </c>
       <c r="B720" s="1" t="s">
@@ -21796,7 +21804,7 @@
       </c>
     </row>
     <row r="721" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A721" s="1">
+      <c r="A721" s="4">
         <v>7620110</v>
       </c>
       <c r="B721" s="1" t="s">
@@ -21829,7 +21837,7 @@
       </c>
     </row>
     <row r="722" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A722" s="1">
+      <c r="A722" s="4">
         <v>7620301</v>
       </c>
       <c r="B722" s="1" t="s">
@@ -21862,7 +21870,7 @@
       </c>
     </row>
     <row r="723" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A723" s="1">
+      <c r="A723" s="4">
         <v>7620301</v>
       </c>
       <c r="B723" s="1" t="s">
@@ -21895,7 +21903,7 @@
       </c>
     </row>
     <row r="724" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A724" s="1">
+      <c r="A724" s="4">
         <v>7640101</v>
       </c>
       <c r="B724" s="1" t="s">
@@ -21928,7 +21936,7 @@
       </c>
     </row>
     <row r="725" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A725" s="1">
+      <c r="A725" s="4">
         <v>7640101</v>
       </c>
       <c r="B725" s="1" t="s">
@@ -21961,7 +21969,7 @@
       </c>
     </row>
     <row r="726" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A726" s="1">
+      <c r="A726" s="4">
         <v>7720301</v>
       </c>
       <c r="B726" s="1" t="s">
@@ -21996,7 +22004,7 @@
       </c>
     </row>
     <row r="727" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A727" s="1">
+      <c r="A727" s="4">
         <v>7720301</v>
       </c>
       <c r="B727" s="1" t="s">
@@ -22031,7 +22039,7 @@
       </c>
     </row>
     <row r="728" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A728" s="1">
+      <c r="A728" s="4">
         <v>7760101</v>
       </c>
       <c r="B728" s="1" t="s">
@@ -22064,7 +22072,7 @@
       </c>
     </row>
     <row r="729" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A729" s="1">
+      <c r="A729" s="4">
         <v>7760101</v>
       </c>
       <c r="B729" s="1" t="s">
@@ -22097,7 +22105,7 @@
       </c>
     </row>
     <row r="730" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A730" s="1">
+      <c r="A730" s="4">
         <v>7850101</v>
       </c>
       <c r="B730" s="1" t="s">
@@ -22130,7 +22138,7 @@
       </c>
     </row>
     <row r="731" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A731" s="1">
+      <c r="A731" s="4">
         <v>7850101</v>
       </c>
       <c r="B731" s="1" t="s">
@@ -22163,7 +22171,7 @@
       </c>
     </row>
     <row r="732" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A732" s="1">
+      <c r="A732" s="4">
         <v>7850103</v>
       </c>
       <c r="B732" s="1" t="s">
@@ -22196,7 +22204,7 @@
       </c>
     </row>
     <row r="733" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A733" s="1">
+      <c r="A733" s="4">
         <v>7850103</v>
       </c>
       <c r="B733" s="1" t="s">
@@ -22229,7 +22237,7 @@
       </c>
     </row>
     <row r="734" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A734" s="1" t="s">
+      <c r="A734" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B734" s="1" t="s">
@@ -22262,7 +22270,7 @@
       </c>
     </row>
     <row r="735" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A735" s="1" t="s">
+      <c r="A735" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B735" s="1" t="s">
@@ -22295,7 +22303,7 @@
       </c>
     </row>
     <row r="736" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A736" s="1" t="s">
+      <c r="A736" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B736" s="1" t="s">
@@ -22324,7 +22332,7 @@
       </c>
     </row>
     <row r="737" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A737" s="1" t="s">
+      <c r="A737" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B737" s="1" t="s">
@@ -22353,7 +22361,7 @@
       </c>
     </row>
     <row r="738" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A738" s="1">
+      <c r="A738" s="4">
         <v>7140114</v>
       </c>
       <c r="B738" s="1" t="s">
@@ -22382,7 +22390,7 @@
       </c>
     </row>
     <row r="739" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A739" s="1">
+      <c r="A739" s="4">
         <v>7140114</v>
       </c>
       <c r="B739" s="1" t="s">
@@ -22411,7 +22419,7 @@
       </c>
     </row>
     <row r="740" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A740" s="1">
+      <c r="A740" s="4">
         <v>7140201</v>
       </c>
       <c r="B740" s="1" t="s">
@@ -22444,7 +22452,7 @@
       </c>
     </row>
     <row r="741" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A741" s="1">
+      <c r="A741" s="4">
         <v>7140201</v>
       </c>
       <c r="B741" s="1" t="s">
@@ -22477,7 +22485,7 @@
       </c>
     </row>
     <row r="742" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A742" s="1">
+      <c r="A742" s="4">
         <v>7140202</v>
       </c>
       <c r="B742" s="1" t="s">
@@ -22506,7 +22514,7 @@
       </c>
     </row>
     <row r="743" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A743" s="1">
+      <c r="A743" s="4">
         <v>7140202</v>
       </c>
       <c r="B743" s="1" t="s">
@@ -22535,7 +22543,7 @@
       </c>
     </row>
     <row r="744" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A744" s="1">
+      <c r="A744" s="4">
         <v>7140205</v>
       </c>
       <c r="B744" s="1" t="s">
@@ -22564,7 +22572,7 @@
       </c>
     </row>
     <row r="745" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A745" s="1">
+      <c r="A745" s="4">
         <v>7140205</v>
       </c>
       <c r="B745" s="1" t="s">
@@ -22593,7 +22601,7 @@
       </c>
     </row>
     <row r="746" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A746" s="1">
+      <c r="A746" s="4">
         <v>7140206</v>
       </c>
       <c r="B746" s="1" t="s">
@@ -22626,7 +22634,7 @@
       </c>
     </row>
     <row r="747" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A747" s="1">
+      <c r="A747" s="4">
         <v>7140206</v>
       </c>
       <c r="B747" s="1" t="s">
@@ -22659,7 +22667,7 @@
       </c>
     </row>
     <row r="748" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A748" s="1">
+      <c r="A748" s="4">
         <v>7140208</v>
       </c>
       <c r="B748" s="1" t="s">
@@ -22688,7 +22696,7 @@
       </c>
     </row>
     <row r="749" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A749" s="1">
+      <c r="A749" s="4">
         <v>7140208</v>
       </c>
       <c r="B749" s="1" t="s">
@@ -22717,7 +22725,7 @@
       </c>
     </row>
     <row r="750" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A750" s="1">
+      <c r="A750" s="4">
         <v>7140209</v>
       </c>
       <c r="B750" s="1" t="s">
@@ -22746,7 +22754,7 @@
       </c>
     </row>
     <row r="751" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A751" s="1">
+      <c r="A751" s="4">
         <v>7140209</v>
       </c>
       <c r="B751" s="1" t="s">
@@ -22775,7 +22783,7 @@
       </c>
     </row>
     <row r="752" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A752" s="1">
+      <c r="A752" s="4">
         <v>7140210</v>
       </c>
       <c r="B752" s="1" t="s">
@@ -22804,7 +22812,7 @@
       </c>
     </row>
     <row r="753" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A753" s="1">
+      <c r="A753" s="4">
         <v>7140210</v>
       </c>
       <c r="B753" s="1" t="s">
@@ -22833,7 +22841,7 @@
       </c>
     </row>
     <row r="754" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A754" s="1">
+      <c r="A754" s="4">
         <v>7140211</v>
       </c>
       <c r="B754" s="1" t="s">
@@ -22862,7 +22870,7 @@
       </c>
     </row>
     <row r="755" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A755" s="1">
+      <c r="A755" s="4">
         <v>7140211</v>
       </c>
       <c r="B755" s="1" t="s">
@@ -22891,7 +22899,7 @@
       </c>
     </row>
     <row r="756" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A756" s="1">
+      <c r="A756" s="4">
         <v>7140212</v>
       </c>
       <c r="B756" s="1" t="s">
@@ -22920,7 +22928,7 @@
       </c>
     </row>
     <row r="757" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A757" s="1">
+      <c r="A757" s="4">
         <v>7140212</v>
       </c>
       <c r="B757" s="1" t="s">
@@ -22949,7 +22957,7 @@
       </c>
     </row>
     <row r="758" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A758" s="1">
+      <c r="A758" s="4">
         <v>7140213</v>
       </c>
       <c r="B758" s="1" t="s">
@@ -22978,7 +22986,7 @@
       </c>
     </row>
     <row r="759" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A759" s="1">
+      <c r="A759" s="4">
         <v>7140213</v>
       </c>
       <c r="B759" s="1" t="s">
@@ -23007,7 +23015,7 @@
       </c>
     </row>
     <row r="760" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A760" s="1">
+      <c r="A760" s="4">
         <v>7140217</v>
       </c>
       <c r="B760" s="1" t="s">
@@ -23036,7 +23044,7 @@
       </c>
     </row>
     <row r="761" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A761" s="1">
+      <c r="A761" s="4">
         <v>7140217</v>
       </c>
       <c r="B761" s="1" t="s">
@@ -23065,7 +23073,7 @@
       </c>
     </row>
     <row r="762" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A762" s="1">
+      <c r="A762" s="4">
         <v>7140218</v>
       </c>
       <c r="B762" s="1" t="s">
@@ -23094,7 +23102,7 @@
       </c>
     </row>
     <row r="763" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A763" s="1">
+      <c r="A763" s="4">
         <v>7140218</v>
       </c>
       <c r="B763" s="1" t="s">
@@ -23123,7 +23131,7 @@
       </c>
     </row>
     <row r="764" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A764" s="1">
+      <c r="A764" s="4">
         <v>7140219</v>
       </c>
       <c r="B764" s="1" t="s">
@@ -23152,7 +23160,7 @@
       </c>
     </row>
     <row r="765" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A765" s="1">
+      <c r="A765" s="4">
         <v>7140219</v>
       </c>
       <c r="B765" s="1" t="s">
@@ -23181,7 +23189,7 @@
       </c>
     </row>
     <row r="766" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A766" s="1">
+      <c r="A766" s="4">
         <v>7140231</v>
       </c>
       <c r="B766" s="1" t="s">
@@ -23214,7 +23222,7 @@
       </c>
     </row>
     <row r="767" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A767" s="1">
+      <c r="A767" s="4">
         <v>7140231</v>
       </c>
       <c r="B767" s="1" t="s">
@@ -23247,7 +23255,7 @@
       </c>
     </row>
     <row r="768" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A768" s="1">
+      <c r="A768" s="4">
         <v>7140247</v>
       </c>
       <c r="B768" s="1" t="s">
@@ -23276,7 +23284,7 @@
       </c>
     </row>
     <row r="769" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A769" s="1">
+      <c r="A769" s="4">
         <v>7140247</v>
       </c>
       <c r="B769" s="1" t="s">
@@ -23305,7 +23313,7 @@
       </c>
     </row>
     <row r="770" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A770" s="1">
+      <c r="A770" s="4">
         <v>7140249</v>
       </c>
       <c r="B770" s="1" t="s">
@@ -23334,7 +23342,7 @@
       </c>
     </row>
     <row r="771" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A771" s="1">
+      <c r="A771" s="4">
         <v>7140249</v>
       </c>
       <c r="B771" s="1" t="s">
@@ -23363,7 +23371,7 @@
       </c>
     </row>
     <row r="772" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A772" s="1">
+      <c r="A772" s="4">
         <v>7220201</v>
       </c>
       <c r="B772" s="1" t="s">
@@ -23396,7 +23404,7 @@
       </c>
     </row>
     <row r="773" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A773" s="1">
+      <c r="A773" s="4">
         <v>7220201</v>
       </c>
       <c r="B773" s="1" t="s">
@@ -23429,7 +23437,7 @@
       </c>
     </row>
     <row r="774" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A774" s="1">
+      <c r="A774" s="4">
         <v>7220204</v>
       </c>
       <c r="B774" s="1" t="s">
@@ -23462,7 +23470,7 @@
       </c>
     </row>
     <row r="775" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A775" s="1">
+      <c r="A775" s="4">
         <v>7220204</v>
       </c>
       <c r="B775" s="1" t="s">
@@ -23495,7 +23503,7 @@
       </c>
     </row>
     <row r="776" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A776" s="1">
+      <c r="A776" s="4">
         <v>7229042</v>
       </c>
       <c r="B776" s="1" t="s">
@@ -23524,7 +23532,7 @@
       </c>
     </row>
     <row r="777" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A777" s="1">
+      <c r="A777" s="4">
         <v>7229042</v>
       </c>
       <c r="B777" s="1" t="s">
@@ -23553,7 +23561,7 @@
       </c>
     </row>
     <row r="778" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A778" s="1">
+      <c r="A778" s="4">
         <v>7310101</v>
       </c>
       <c r="B778" s="1" t="s">
@@ -23582,7 +23590,7 @@
       </c>
     </row>
     <row r="779" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A779" s="1">
+      <c r="A779" s="4">
         <v>7310101</v>
       </c>
       <c r="B779" s="1" t="s">
@@ -23611,7 +23619,7 @@
       </c>
     </row>
     <row r="780" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A780" s="1">
+      <c r="A780" s="4">
         <v>7310104</v>
       </c>
       <c r="B780" s="1" t="s">
@@ -23640,7 +23648,7 @@
       </c>
     </row>
     <row r="781" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A781" s="1">
+      <c r="A781" s="4">
         <v>7310104</v>
       </c>
       <c r="B781" s="1" t="s">
@@ -23669,7 +23677,7 @@
       </c>
     </row>
     <row r="782" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A782" s="1">
+      <c r="A782" s="4">
         <v>7310109</v>
       </c>
       <c r="B782" s="1" t="s">
@@ -23698,7 +23706,7 @@
       </c>
     </row>
     <row r="783" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A783" s="1">
+      <c r="A783" s="4">
         <v>7310109</v>
       </c>
       <c r="B783" s="1" t="s">
@@ -23727,7 +23735,7 @@
       </c>
     </row>
     <row r="784" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A784" s="1">
+      <c r="A784" s="4">
         <v>7310110</v>
       </c>
       <c r="B784" s="1" t="s">
@@ -23756,7 +23764,7 @@
       </c>
     </row>
     <row r="785" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A785" s="1">
+      <c r="A785" s="4">
         <v>7310110</v>
       </c>
       <c r="B785" s="1" t="s">
@@ -23785,7 +23793,7 @@
       </c>
     </row>
     <row r="786" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A786" s="1">
+      <c r="A786" s="4">
         <v>7310201</v>
       </c>
       <c r="B786" s="1" t="s">
@@ -23814,7 +23822,7 @@
       </c>
     </row>
     <row r="787" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A787" s="1">
+      <c r="A787" s="4">
         <v>7310201</v>
       </c>
       <c r="B787" s="1" t="s">
@@ -23843,7 +23851,7 @@
       </c>
     </row>
     <row r="788" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A788" s="1">
+      <c r="A788" s="4">
         <v>7310205</v>
       </c>
       <c r="B788" s="1" t="s">
@@ -23872,7 +23880,7 @@
       </c>
     </row>
     <row r="789" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A789" s="1">
+      <c r="A789" s="4">
         <v>7310205</v>
       </c>
       <c r="B789" s="1" t="s">
@@ -23901,7 +23909,7 @@
       </c>
     </row>
     <row r="790" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A790" s="1">
+      <c r="A790" s="4">
         <v>7310403</v>
       </c>
       <c r="B790" s="1" t="s">
@@ -23930,7 +23938,7 @@
       </c>
     </row>
     <row r="791" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A791" s="1">
+      <c r="A791" s="4">
         <v>7310403</v>
       </c>
       <c r="B791" s="1" t="s">
@@ -23959,7 +23967,7 @@
       </c>
     </row>
     <row r="792" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A792" s="1">
+      <c r="A792" s="4">
         <v>7310601</v>
       </c>
       <c r="B792" s="1" t="s">
@@ -23988,7 +23996,7 @@
       </c>
     </row>
     <row r="793" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A793" s="1">
+      <c r="A793" s="4">
         <v>7310601</v>
       </c>
       <c r="B793" s="1" t="s">
@@ -24017,7 +24025,7 @@
       </c>
     </row>
     <row r="794" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A794" s="1">
+      <c r="A794" s="4">
         <v>7310630</v>
       </c>
       <c r="B794" s="1" t="s">
@@ -24046,7 +24054,7 @@
       </c>
     </row>
     <row r="795" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A795" s="1">
+      <c r="A795" s="4">
         <v>7310630</v>
       </c>
       <c r="B795" s="1" t="s">
@@ -24075,7 +24083,7 @@
       </c>
     </row>
     <row r="796" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A796" s="1">
+      <c r="A796" s="4">
         <v>7340101</v>
       </c>
       <c r="B796" s="1" t="s">
@@ -24104,7 +24112,7 @@
       </c>
     </row>
     <row r="797" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A797" s="1">
+      <c r="A797" s="4">
         <v>7340101</v>
       </c>
       <c r="B797" s="1" t="s">
@@ -24133,7 +24141,7 @@
       </c>
     </row>
     <row r="798" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A798" s="1">
+      <c r="A798" s="4">
         <v>7340115</v>
       </c>
       <c r="B798" s="1" t="s">
@@ -24162,7 +24170,7 @@
       </c>
     </row>
     <row r="799" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A799" s="1">
+      <c r="A799" s="4">
         <v>7340115</v>
       </c>
       <c r="B799" s="1" t="s">
@@ -24191,7 +24199,7 @@
       </c>
     </row>
     <row r="800" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A800" s="1">
+      <c r="A800" s="4">
         <v>7340122</v>
       </c>
       <c r="B800" s="1" t="s">
@@ -24220,7 +24228,7 @@
       </c>
     </row>
     <row r="801" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A801" s="1">
+      <c r="A801" s="4">
         <v>7340122</v>
       </c>
       <c r="B801" s="1" t="s">
@@ -24249,7 +24257,7 @@
       </c>
     </row>
     <row r="802" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A802" s="1">
+      <c r="A802" s="4">
         <v>7340201</v>
       </c>
       <c r="B802" s="1" t="s">
@@ -24278,7 +24286,7 @@
       </c>
     </row>
     <row r="803" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A803" s="1">
+      <c r="A803" s="4">
         <v>7340201</v>
       </c>
       <c r="B803" s="1" t="s">
@@ -24307,7 +24315,7 @@
       </c>
     </row>
     <row r="804" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A804" s="1">
+      <c r="A804" s="4">
         <v>7340205</v>
       </c>
       <c r="B804" s="1" t="s">
@@ -24336,7 +24344,7 @@
       </c>
     </row>
     <row r="805" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A805" s="1">
+      <c r="A805" s="4">
         <v>7340205</v>
       </c>
       <c r="B805" s="1" t="s">
@@ -24365,7 +24373,7 @@
       </c>
     </row>
     <row r="806" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A806" s="1">
+      <c r="A806" s="4">
         <v>7340301</v>
       </c>
       <c r="B806" s="1" t="s">
@@ -24394,7 +24402,7 @@
       </c>
     </row>
     <row r="807" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A807" s="1">
+      <c r="A807" s="4">
         <v>7340301</v>
       </c>
       <c r="B807" s="1" t="s">
@@ -24423,7 +24431,7 @@
       </c>
     </row>
     <row r="808" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A808" s="1">
+      <c r="A808" s="4">
         <v>7340302</v>
       </c>
       <c r="B808" s="1" t="s">
@@ -24452,7 +24460,7 @@
       </c>
     </row>
     <row r="809" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A809" s="1">
+      <c r="A809" s="4">
         <v>7340302</v>
       </c>
       <c r="B809" s="1" t="s">
@@ -24481,7 +24489,7 @@
       </c>
     </row>
     <row r="810" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A810" s="1">
+      <c r="A810" s="4">
         <v>7380101</v>
       </c>
       <c r="B810" s="1" t="s">
@@ -24510,7 +24518,7 @@
       </c>
     </row>
     <row r="811" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A811" s="1">
+      <c r="A811" s="4">
         <v>7380101</v>
       </c>
       <c r="B811" s="1" t="s">
@@ -24539,7 +24547,7 @@
       </c>
     </row>
     <row r="812" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A812" s="1">
+      <c r="A812" s="4">
         <v>7380102</v>
       </c>
       <c r="B812" s="1" t="s">
@@ -24568,7 +24576,7 @@
       </c>
     </row>
     <row r="813" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A813" s="1">
+      <c r="A813" s="4">
         <v>7380102</v>
       </c>
       <c r="B813" s="1" t="s">
@@ -24597,7 +24605,7 @@
       </c>
     </row>
     <row r="814" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A814" s="1">
+      <c r="A814" s="4">
         <v>7380103</v>
       </c>
       <c r="B814" s="1" t="s">
@@ -24626,7 +24634,7 @@
       </c>
     </row>
     <row r="815" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A815" s="1">
+      <c r="A815" s="4">
         <v>7380103</v>
       </c>
       <c r="B815" s="1" t="s">
@@ -24655,7 +24663,7 @@
       </c>
     </row>
     <row r="816" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A816" s="1">
+      <c r="A816" s="4">
         <v>7380107</v>
       </c>
       <c r="B816" s="1" t="s">
@@ -24684,7 +24692,7 @@
       </c>
     </row>
     <row r="817" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A817" s="1">
+      <c r="A817" s="4">
         <v>7380107</v>
       </c>
       <c r="B817" s="1" t="s">
@@ -24713,7 +24721,7 @@
       </c>
     </row>
     <row r="818" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A818" s="1">
+      <c r="A818" s="4">
         <v>7420201</v>
       </c>
       <c r="B818" s="1" t="s">
@@ -24742,7 +24750,7 @@
       </c>
     </row>
     <row r="819" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A819" s="1">
+      <c r="A819" s="4">
         <v>7420201</v>
       </c>
       <c r="B819" s="1" t="s">
@@ -24771,7 +24779,7 @@
       </c>
     </row>
     <row r="820" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A820" s="1">
+      <c r="A820" s="4">
         <v>7480101</v>
       </c>
       <c r="B820" s="1" t="s">
@@ -24800,7 +24808,7 @@
       </c>
     </row>
     <row r="821" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A821" s="1">
+      <c r="A821" s="4">
         <v>7480101</v>
       </c>
       <c r="B821" s="1" t="s">
@@ -24829,7 +24837,7 @@
       </c>
     </row>
     <row r="822" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A822" s="1">
+      <c r="A822" s="4">
         <v>7480201</v>
       </c>
       <c r="B822" s="1" t="s">
@@ -24858,7 +24866,7 @@
       </c>
     </row>
     <row r="823" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A823" s="1">
+      <c r="A823" s="4">
         <v>7480201</v>
       </c>
       <c r="B823" s="1" t="s">
@@ -24887,7 +24895,7 @@
       </c>
     </row>
     <row r="824" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A824" s="1">
+      <c r="A824" s="4">
         <v>7510205</v>
       </c>
       <c r="B824" s="1" t="s">
@@ -24916,7 +24924,7 @@
       </c>
     </row>
     <row r="825" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A825" s="1">
+      <c r="A825" s="4">
         <v>7510205</v>
       </c>
       <c r="B825" s="1" t="s">
@@ -24945,7 +24953,7 @@
       </c>
     </row>
     <row r="826" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A826" s="1">
+      <c r="A826" s="4">
         <v>7510206</v>
       </c>
       <c r="B826" s="1" t="s">
@@ -24974,7 +24982,7 @@
       </c>
     </row>
     <row r="827" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A827" s="1">
+      <c r="A827" s="4">
         <v>7510206</v>
       </c>
       <c r="B827" s="1" t="s">
@@ -25003,7 +25011,7 @@
       </c>
     </row>
     <row r="828" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A828" s="1">
+      <c r="A828" s="4">
         <v>7510301</v>
       </c>
       <c r="B828" s="1" t="s">
@@ -25032,7 +25040,7 @@
       </c>
     </row>
     <row r="829" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A829" s="1">
+      <c r="A829" s="4">
         <v>7510301</v>
       </c>
       <c r="B829" s="1" t="s">
@@ -25061,7 +25069,7 @@
       </c>
     </row>
     <row r="830" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A830" s="1">
+      <c r="A830" s="4">
         <v>7510302</v>
       </c>
       <c r="B830" s="1" t="s">
@@ -25090,7 +25098,7 @@
       </c>
     </row>
     <row r="831" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A831" s="1">
+      <c r="A831" s="4">
         <v>7510302</v>
       </c>
       <c r="B831" s="1" t="s">
@@ -25119,7 +25127,7 @@
       </c>
     </row>
     <row r="832" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A832" s="1">
+      <c r="A832" s="4">
         <v>7510303</v>
       </c>
       <c r="B832" s="1" t="s">
@@ -25148,7 +25156,7 @@
       </c>
     </row>
     <row r="833" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A833" s="1">
+      <c r="A833" s="4">
         <v>7510303</v>
       </c>
       <c r="B833" s="1" t="s">
@@ -25177,7 +25185,7 @@
       </c>
     </row>
     <row r="834" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A834" s="1">
+      <c r="A834" s="4">
         <v>7520207</v>
       </c>
       <c r="B834" s="1" t="s">
@@ -25206,7 +25214,7 @@
       </c>
     </row>
     <row r="835" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A835" s="1">
+      <c r="A835" s="4">
         <v>7520207</v>
       </c>
       <c r="B835" s="1" t="s">
@@ -25235,7 +25243,7 @@
       </c>
     </row>
     <row r="836" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A836" s="1">
+      <c r="A836" s="4">
         <v>7520216</v>
       </c>
       <c r="B836" s="1" t="s">
@@ -25264,7 +25272,7 @@
       </c>
     </row>
     <row r="837" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A837" s="1">
+      <c r="A837" s="4">
         <v>7520216</v>
       </c>
       <c r="B837" s="1" t="s">
@@ -25293,7 +25301,7 @@
       </c>
     </row>
     <row r="838" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A838" s="1">
+      <c r="A838" s="4">
         <v>7540101</v>
       </c>
       <c r="B838" s="1" t="s">
@@ -25322,7 +25330,7 @@
       </c>
     </row>
     <row r="839" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A839" s="1">
+      <c r="A839" s="4">
         <v>7540101</v>
       </c>
       <c r="B839" s="1" t="s">
@@ -25351,7 +25359,7 @@
       </c>
     </row>
     <row r="840" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A840" s="1">
+      <c r="A840" s="4">
         <v>7580101</v>
       </c>
       <c r="B840" s="1" t="s">
@@ -25382,7 +25390,7 @@
       </c>
     </row>
     <row r="841" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A841" s="1">
+      <c r="A841" s="4">
         <v>7580101</v>
       </c>
       <c r="B841" s="1" t="s">
@@ -25413,7 +25421,7 @@
       </c>
     </row>
     <row r="842" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A842" s="1">
+      <c r="A842" s="4">
         <v>7580201</v>
       </c>
       <c r="B842" s="1" t="s">
@@ -25442,7 +25450,7 @@
       </c>
     </row>
     <row r="843" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A843" s="1">
+      <c r="A843" s="4">
         <v>7580201</v>
       </c>
       <c r="B843" s="1" t="s">
@@ -25471,7 +25479,7 @@
       </c>
     </row>
     <row r="844" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A844" s="1">
+      <c r="A844" s="4">
         <v>7580205</v>
       </c>
       <c r="B844" s="1" t="s">
@@ -25500,7 +25508,7 @@
       </c>
     </row>
     <row r="845" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A845" s="1">
+      <c r="A845" s="4">
         <v>7580205</v>
       </c>
       <c r="B845" s="1" t="s">
@@ -25529,7 +25537,7 @@
       </c>
     </row>
     <row r="846" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A846" s="1">
+      <c r="A846" s="4">
         <v>7580301</v>
       </c>
       <c r="B846" s="1" t="s">
@@ -25558,7 +25566,7 @@
       </c>
     </row>
     <row r="847" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A847" s="1">
+      <c r="A847" s="4">
         <v>7580301</v>
       </c>
       <c r="B847" s="1" t="s">
@@ -25587,7 +25595,7 @@
       </c>
     </row>
     <row r="848" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A848" s="1">
+      <c r="A848" s="4">
         <v>7620105</v>
       </c>
       <c r="B848" s="1" t="s">
@@ -25616,7 +25624,7 @@
       </c>
     </row>
     <row r="849" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A849" s="1">
+      <c r="A849" s="4">
         <v>7620105</v>
       </c>
       <c r="B849" s="1" t="s">
@@ -25645,7 +25653,7 @@
       </c>
     </row>
     <row r="850" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A850" s="1">
+      <c r="A850" s="4">
         <v>7620109</v>
       </c>
       <c r="B850" s="1" t="s">
@@ -25674,7 +25682,7 @@
       </c>
     </row>
     <row r="851" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A851" s="1">
+      <c r="A851" s="4">
         <v>7620109</v>
       </c>
       <c r="B851" s="1" t="s">
@@ -25703,7 +25711,7 @@
       </c>
     </row>
     <row r="852" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A852" s="1">
+      <c r="A852" s="4">
         <v>7620110</v>
       </c>
       <c r="B852" s="1" t="s">
@@ -25732,7 +25740,7 @@
       </c>
     </row>
     <row r="853" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A853" s="1">
+      <c r="A853" s="4">
         <v>7620110</v>
       </c>
       <c r="B853" s="1" t="s">
@@ -25761,7 +25769,7 @@
       </c>
     </row>
     <row r="854" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A854" s="1">
+      <c r="A854" s="4">
         <v>7620301</v>
       </c>
       <c r="B854" s="1" t="s">
@@ -25790,7 +25798,7 @@
       </c>
     </row>
     <row r="855" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A855" s="1">
+      <c r="A855" s="4">
         <v>7620301</v>
       </c>
       <c r="B855" s="1" t="s">
@@ -25819,7 +25827,7 @@
       </c>
     </row>
     <row r="856" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A856" s="1">
+      <c r="A856" s="4">
         <v>7640101</v>
       </c>
       <c r="B856" s="1" t="s">
@@ -25848,7 +25856,7 @@
       </c>
     </row>
     <row r="857" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A857" s="1">
+      <c r="A857" s="4">
         <v>7640101</v>
       </c>
       <c r="B857" s="1" t="s">
@@ -25877,7 +25885,7 @@
       </c>
     </row>
     <row r="858" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A858" s="1">
+      <c r="A858" s="4">
         <v>7720301</v>
       </c>
       <c r="B858" s="1" t="s">
@@ -25906,7 +25914,7 @@
       </c>
     </row>
     <row r="859" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A859" s="1">
+      <c r="A859" s="4">
         <v>7720301</v>
       </c>
       <c r="B859" s="1" t="s">
@@ -25935,7 +25943,7 @@
       </c>
     </row>
     <row r="860" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A860" s="1">
+      <c r="A860" s="4">
         <v>7760101</v>
       </c>
       <c r="B860" s="1" t="s">
@@ -25964,7 +25972,7 @@
       </c>
     </row>
     <row r="861" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A861" s="1">
+      <c r="A861" s="4">
         <v>7760101</v>
       </c>
       <c r="B861" s="1" t="s">
@@ -25993,7 +26001,7 @@
       </c>
     </row>
     <row r="862" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A862" s="1">
+      <c r="A862" s="4">
         <v>7850101</v>
       </c>
       <c r="B862" s="1" t="s">
@@ -26022,7 +26030,7 @@
       </c>
     </row>
     <row r="863" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A863" s="1">
+      <c r="A863" s="4">
         <v>7850101</v>
       </c>
       <c r="B863" s="1" t="s">
@@ -26051,7 +26059,7 @@
       </c>
     </row>
     <row r="864" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A864" s="1">
+      <c r="A864" s="4">
         <v>7850103</v>
       </c>
       <c r="B864" s="1" t="s">
@@ -26080,7 +26088,7 @@
       </c>
     </row>
     <row r="865" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A865" s="1">
+      <c r="A865" s="4">
         <v>7850103</v>
       </c>
       <c r="B865" s="1" t="s">
@@ -26109,7 +26117,7 @@
       </c>
     </row>
     <row r="866" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A866" s="1" t="s">
+      <c r="A866" s="4" t="s">
         <v>137</v>
       </c>
       <c r="B866" s="1" t="s">
@@ -26138,7 +26146,7 @@
       </c>
     </row>
     <row r="867" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A867" s="1" t="s">
+      <c r="A867" s="4" t="s">
         <v>137</v>
       </c>
       <c r="B867" s="1" t="s">
@@ -26167,7 +26175,7 @@
       </c>
     </row>
     <row r="868" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A868" s="1" t="s">
+      <c r="A868" s="4" t="s">
         <v>138</v>
       </c>
       <c r="B868" s="1" t="s">
@@ -26200,7 +26208,7 @@
       </c>
     </row>
     <row r="869" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A869" s="1" t="s">
+      <c r="A869" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B869" s="1" t="s">
@@ -26229,7 +26237,7 @@
       </c>
     </row>
     <row r="870" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A870" s="1" t="s">
+      <c r="A870" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B870" s="1" t="s">
@@ -26258,7 +26266,7 @@
       </c>
     </row>
     <row r="871" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A871" s="1" t="s">
+      <c r="A871" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B871" s="1" t="s">
@@ -26287,7 +26295,7 @@
       </c>
     </row>
     <row r="872" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A872" s="1" t="s">
+      <c r="A872" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B872" s="1" t="s">
@@ -26316,7 +26324,7 @@
       </c>
     </row>
     <row r="873" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A873" s="1">
+      <c r="A873" s="4">
         <v>7140201</v>
       </c>
       <c r="B873" s="1" t="s">
@@ -26349,7 +26357,7 @@
       </c>
     </row>
     <row r="874" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A874" s="1">
+      <c r="A874" s="4">
         <v>7140201</v>
       </c>
       <c r="B874" s="1" t="s">
@@ -26382,7 +26390,7 @@
       </c>
     </row>
     <row r="875" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A875" s="1">
+      <c r="A875" s="4">
         <v>7140206</v>
       </c>
       <c r="B875" s="1" t="s">
@@ -26415,7 +26423,7 @@
       </c>
     </row>
     <row r="876" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A876" s="1">
+      <c r="A876" s="4">
         <v>7140206</v>
       </c>
       <c r="B876" s="1" t="s">
@@ -26448,7 +26456,7 @@
       </c>
     </row>
     <row r="877" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A877" s="1">
+      <c r="A877" s="4">
         <v>7580101</v>
       </c>
       <c r="B877" s="1" t="s">
@@ -26479,7 +26487,7 @@
       </c>
     </row>
     <row r="878" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A878" s="1">
+      <c r="A878" s="4">
         <v>7580101</v>
       </c>
       <c r="B878" s="1" t="s">
@@ -26510,7 +26518,7 @@
       </c>
     </row>
     <row r="879" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A879" s="1" t="s">
+      <c r="A879" s="4" t="s">
         <v>161</v>
       </c>
       <c r="B879" s="1" t="s">
@@ -26539,7 +26547,7 @@
       </c>
     </row>
     <row r="880" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A880" s="1" t="s">
+      <c r="A880" s="4" t="s">
         <v>161</v>
       </c>
       <c r="B880" s="1" t="s">
@@ -26568,7 +26576,7 @@
       </c>
     </row>
     <row r="881" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A881" s="1" t="s">
+      <c r="A881" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B881" s="1" t="s">
@@ -26597,7 +26605,7 @@
       </c>
     </row>
     <row r="882" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A882" s="1" t="s">
+      <c r="A882" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B882" s="1" t="s">
@@ -26626,7 +26634,7 @@
       </c>
     </row>
     <row r="883" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A883" s="1" t="s">
+      <c r="A883" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B883" s="1" t="s">
@@ -26655,7 +26663,7 @@
       </c>
     </row>
     <row r="884" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A884" s="1" t="s">
+      <c r="A884" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B884" s="1" t="s">
@@ -26684,7 +26692,7 @@
       </c>
     </row>
     <row r="885" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A885" s="1" t="s">
+      <c r="A885" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B885" s="1" t="s">
@@ -26713,7 +26721,7 @@
       </c>
     </row>
     <row r="886" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A886" s="1" t="s">
+      <c r="A886" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B886" s="1" t="s">
@@ -26742,7 +26750,7 @@
       </c>
     </row>
     <row r="887" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A887" s="1" t="s">
+      <c r="A887" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B887" s="1" t="s">
@@ -26771,7 +26779,7 @@
       </c>
     </row>
     <row r="888" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A888" s="1" t="s">
+      <c r="A888" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B888" s="1" t="s">
@@ -26800,7 +26808,7 @@
       </c>
     </row>
     <row r="889" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A889" s="1" t="s">
+      <c r="A889" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B889" s="1" t="s">
@@ -26829,7 +26837,7 @@
       </c>
     </row>
     <row r="890" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A890" s="1" t="s">
+      <c r="A890" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B890" s="1" t="s">
@@ -26858,7 +26866,7 @@
       </c>
     </row>
     <row r="891" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A891" s="1" t="s">
+      <c r="A891" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B891" s="1" t="s">
@@ -26891,7 +26899,7 @@
       </c>
     </row>
     <row r="892" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A892" s="1" t="s">
+      <c r="A892" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B892" s="1" t="s">
@@ -26924,7 +26932,7 @@
       </c>
     </row>
     <row r="893" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A893" s="1" t="s">
+      <c r="A893" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B893" s="1" t="s">
@@ -26957,7 +26965,7 @@
       </c>
     </row>
     <row r="894" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A894" s="1" t="s">
+      <c r="A894" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B894" s="1" t="s">
@@ -26990,7 +26998,7 @@
       </c>
     </row>
     <row r="895" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A895" s="1" t="s">
+      <c r="A895" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B895" s="1" t="s">
@@ -27023,7 +27031,7 @@
       </c>
     </row>
     <row r="896" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A896" s="1" t="s">
+      <c r="A896" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B896" s="1" t="s">
@@ -27056,7 +27064,7 @@
       </c>
     </row>
     <row r="897" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A897" s="1" t="s">
+      <c r="A897" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B897" s="1" t="s">
@@ -27089,7 +27097,7 @@
       </c>
     </row>
     <row r="898" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A898" s="1" t="s">
+      <c r="A898" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B898" s="1" t="s">
@@ -27122,7 +27130,7 @@
       </c>
     </row>
     <row r="899" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A899" s="1" t="s">
+      <c r="A899" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B899" s="1" t="s">
@@ -27155,7 +27163,7 @@
       </c>
     </row>
     <row r="900" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A900" s="1" t="s">
+      <c r="A900" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B900" s="1" t="s">
@@ -27188,7 +27196,7 @@
       </c>
     </row>
     <row r="901" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A901" s="1" t="s">
+      <c r="A901" s="4" t="s">
         <v>161</v>
       </c>
       <c r="B901" s="1" t="s">
@@ -27217,7 +27225,7 @@
       </c>
     </row>
     <row r="902" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A902" s="1" t="s">
+      <c r="A902" s="4" t="s">
         <v>161</v>
       </c>
       <c r="B902" s="1" t="s">
@@ -27246,7 +27254,7 @@
       </c>
     </row>
     <row r="903" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A903" s="1" t="s">
+      <c r="A903" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B903" s="1" t="s">
@@ -27275,7 +27283,7 @@
       </c>
     </row>
     <row r="904" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A904" s="1" t="s">
+      <c r="A904" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B904" s="1" t="s">
@@ -27304,7 +27312,7 @@
       </c>
     </row>
     <row r="905" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A905" s="1" t="s">
+      <c r="A905" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B905" s="1" t="s">
@@ -27333,7 +27341,7 @@
       </c>
     </row>
     <row r="906" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A906" s="1" t="s">
+      <c r="A906" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B906" s="1" t="s">
@@ -27362,7 +27370,7 @@
       </c>
     </row>
     <row r="907" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A907" s="1" t="s">
+      <c r="A907" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B907" s="1" t="s">
@@ -27391,7 +27399,7 @@
       </c>
     </row>
     <row r="908" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A908" s="1" t="s">
+      <c r="A908" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B908" s="1" t="s">
@@ -27420,7 +27428,7 @@
       </c>
     </row>
     <row r="909" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A909" s="1" t="s">
+      <c r="A909" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B909" s="1" t="s">
@@ -27449,7 +27457,7 @@
       </c>
     </row>
     <row r="910" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A910" s="1" t="s">
+      <c r="A910" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B910" s="1" t="s">
@@ -27478,7 +27486,7 @@
       </c>
     </row>
     <row r="911" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A911" s="1" t="s">
+      <c r="A911" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B911" s="1" t="s">
@@ -27507,7 +27515,7 @@
       </c>
     </row>
     <row r="912" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A912" s="1" t="s">
+      <c r="A912" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B912" s="1" t="s">
@@ -27536,7 +27544,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O912" xr:uid="{D2A16004-149F-469E-9454-450BC0FDCCAF}"/>
+  <autoFilter ref="A1:O912" xr:uid="{D2A16004-149F-469E-9454-450BC0FDCCAF}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2026"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>